--- a/sample-config_analysis.xlsx
+++ b/sample-config_analysis.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crypto &amp; System" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Security Issues" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CIS v8 Mapping" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Security Rules'!$A$1:$AC$1</definedName>
@@ -24,7 +25,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Address Groups'!$A$1:$F$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Service Objects'!$A$2:$E$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Zones'!$A$1:$F$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Security Issues'!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Security Issues'!$A$1:$I$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -33,7 +34,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -134,8 +135,31 @@
       <color rgb="00595959"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0017375E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -182,6 +206,21 @@
         <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0017375E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E4057"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9F9F9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -209,7 +248,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -302,8 +341,32 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -692,7 +755,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-04-28 22:01:42    Source file: sample-config.xml</t>
+          <t>Generated: 2026-04-29 02:15:20    Source file: sample-config.xml</t>
         </is>
       </c>
     </row>
@@ -1205,6 +1268,3462 @@
   <mergeCells count="2">
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F155"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="39" t="inlineStr">
+        <is>
+          <t>CIS Controls v8 — Finding Cross-Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Each CIS safeguard lists all findings from this config that map to it, with count and severity breakdown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="40" t="inlineStr">
+        <is>
+          <t>CIS 3.10 — Encrypt Sensitive Data in Transit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="41" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="B5" s="41" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C5" s="41" t="inlineStr">
+        <is>
+          <t>Rule / Object</t>
+        </is>
+      </c>
+      <c r="D5" s="41" t="inlineStr">
+        <is>
+          <t>Config Line(s)</t>
+        </is>
+      </c>
+      <c r="E5" s="41" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F5" s="41" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>Weak IKE Encryption</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
+          <t>IKE Profile: weak-ike-profile</t>
+        </is>
+      </c>
+      <c r="D6" s="42" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="inlineStr">
+        <is>
+          <t>IKE crypto profile 'weak-ike-profile' uses 3DES encryption.</t>
+        </is>
+      </c>
+      <c r="F6" s="18" t="inlineStr">
+        <is>
+          <t>Replace 3DES with AES-256-GCM or AES-256-CBC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>Weak IKE Hash/PRF</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>IKE Profile: weak-ike-profile</t>
+        </is>
+      </c>
+      <c r="D7" s="43" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>IKE crypto profile 'weak-ike-profile' uses MD5 for integrity/PRF.</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr">
+        <is>
+          <t>Replace MD5 with SHA-256, SHA-384, or SHA-512.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>Weak IKE DH Group</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="inlineStr">
+        <is>
+          <t>IKE Profile: weak-ike-profile</t>
+        </is>
+      </c>
+      <c r="D8" s="42" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="inlineStr">
+        <is>
+          <t>IKE crypto profile 'weak-ike-profile' includes group2 (insufficient key size).</t>
+        </is>
+      </c>
+      <c r="F8" s="18" t="inlineStr">
+        <is>
+          <t>Use DH Group 14 (2048-bit) minimum; prefer Group 19/20 (ECDH-256/384).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>Weak IPSec Encryption</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>IPSec Profile: weak-ipsec-profile</t>
+        </is>
+      </c>
+      <c r="D9" s="43" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>IPSec crypto profile 'weak-ipsec-profile' uses 3DES for ESP encryption.</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr">
+        <is>
+          <t>Replace 3DES with AES-256-GCM (preferred) or AES-256-CBC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>Weak IPSec Authentication</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>IPSec Profile: weak-ipsec-profile</t>
+        </is>
+      </c>
+      <c r="D10" s="42" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E10" s="18" t="inlineStr">
+        <is>
+          <t>IPSec crypto profile 'weak-ipsec-profile' uses MD5 for ESP authentication.</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>Replace MD5 with SHA-256 or higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B11" s="21" t="inlineStr">
+        <is>
+          <t>Weak IPSec DH Group (PFS)</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>IPSec Profile: weak-ipsec-profile</t>
+        </is>
+      </c>
+      <c r="D11" s="43" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>IPSec profile 'weak-ipsec-profile' uses group2 for Perfect Forward Secrecy.</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr">
+        <is>
+          <t>Use DH Group 14 minimum for PFS; prefer Group 19/20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>Weak Minimum TLS Version</t>
+        </is>
+      </c>
+      <c r="C12" s="18" t="inlineStr">
+        <is>
+          <t>SSL/TLS Profile: old-tls-profile</t>
+        </is>
+      </c>
+      <c r="D12" s="42" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="inlineStr">
+        <is>
+          <t>SSL/TLS profile 'old-tls-profile' allows TLS1.0 connections.</t>
+        </is>
+      </c>
+      <c r="F12" s="18" t="inlineStr">
+        <is>
+          <t>Set minimum version to TLS 1.2; prefer TLS 1.3 where supported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B13" s="21" t="inlineStr">
+        <is>
+          <t>Weak IKE Hash/PRF</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>IKE Profile: weak-ike-profile</t>
+        </is>
+      </c>
+      <c r="D13" s="43" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="inlineStr">
+        <is>
+          <t>IKE crypto profile 'weak-ike-profile' uses SHA1 for integrity/PRF.</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr">
+        <is>
+          <t>Replace SHA1 with SHA-256, SHA-384, or SHA-512.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="40" t="inlineStr">
+        <is>
+          <t>CIS 4.2 — Secure Configuration Process for Network Infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="41" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="B16" s="41" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C16" s="41" t="inlineStr">
+        <is>
+          <t>Rule / Object</t>
+        </is>
+      </c>
+      <c r="D16" s="41" t="inlineStr">
+        <is>
+          <t>Config Line(s)</t>
+        </is>
+      </c>
+      <c r="E16" s="41" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F16" s="41" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B17" s="21" t="inlineStr">
+        <is>
+          <t>HTTP Management Enabled</t>
+        </is>
+      </c>
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="D17" s="43" t="inlineStr"/>
+      <c r="E17" s="21" t="inlineStr">
+        <is>
+          <t>HTTP access to the management interface is enabled (cleartext).</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr">
+        <is>
+          <t>Disable HTTP management: set service/disable-http to yes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>Telnet Management Enabled</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="D18" s="42" t="inlineStr"/>
+      <c r="E18" s="18" t="inlineStr">
+        <is>
+          <t>Telnet access to the management interface is enabled (cleartext).</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>Disable Telnet management: set service/disable-telnet to yes. Use SSH instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>Negated Source Address</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>Block-Except-Partners</t>
+        </is>
+      </c>
+      <c r="D19" s="43" t="inlineStr">
+        <is>
+          <t>305-313</t>
+        </is>
+      </c>
+      <c r="E19" s="21" t="inlineStr">
+        <is>
+          <t>Rule uses a negated source — all IPs *except* the listed ones match.</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr">
+        <is>
+          <t>Confirm this is intentional; consider rewriting as explicit allow/deny pairs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>Potential Shadow Rule</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>Allow-Partner-Access</t>
+        </is>
+      </c>
+      <c r="D20" s="42" t="inlineStr">
+        <is>
+          <t>235-245</t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="inlineStr">
+        <is>
+          <t>Rule may never be matched because rule 'Temp-AllowAll-Legacy' (#2) already covers its traffic.</t>
+        </is>
+      </c>
+      <c r="F20" s="18" t="inlineStr">
+        <is>
+          <t>Review rule order and remove or reorder as appropriate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>Potential Shadow Rule</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>Allow-RDP-Everywhere</t>
+        </is>
+      </c>
+      <c r="D21" s="43" t="inlineStr">
+        <is>
+          <t>249-259</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>Rule may never be matched because rule 'Temp-AllowAll-Legacy' (#2) already covers its traffic.</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr">
+        <is>
+          <t>Review rule order and remove or reorder as appropriate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>Potential Shadow Rule</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="inlineStr">
+        <is>
+          <t>Internal-DMZ-Access</t>
+        </is>
+      </c>
+      <c r="D22" s="42" t="inlineStr">
+        <is>
+          <t>263-270</t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="inlineStr">
+        <is>
+          <t>Rule may never be matched because rule 'Temp-AllowAll-Legacy' (#2) already covers its traffic.</t>
+        </is>
+      </c>
+      <c r="F22" s="18" t="inlineStr">
+        <is>
+          <t>Review rule order and remove or reorder as appropriate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B23" s="21" t="inlineStr">
+        <is>
+          <t>Potential Shadow Rule</t>
+        </is>
+      </c>
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>Allow-Outbound-Internet</t>
+        </is>
+      </c>
+      <c r="D23" s="43" t="inlineStr">
+        <is>
+          <t>290-301</t>
+        </is>
+      </c>
+      <c r="E23" s="21" t="inlineStr">
+        <is>
+          <t>Rule may never be matched because rule 'Temp-AllowAll-Legacy' (#2) already covers its traffic.</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr">
+        <is>
+          <t>Review rule order and remove or reorder as appropriate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>SNMPv2c Enabled</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="inlineStr">
+        <is>
+          <t>SNMP</t>
+        </is>
+      </c>
+      <c r="D24" s="42" t="inlineStr"/>
+      <c r="E24" s="18" t="inlineStr">
+        <is>
+          <t>SNMPv2c is enabled; community strings are transmitted in cleartext.</t>
+        </is>
+      </c>
+      <c r="F24" s="18" t="inlineStr">
+        <is>
+          <t>Migrate to SNMPv3 with authPriv. If SNMPv2c is required, restrict source IPs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="B25" s="21" t="inlineStr">
+        <is>
+          <t>Disabled Rule</t>
+        </is>
+      </c>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>Old-FTP-Rule</t>
+        </is>
+      </c>
+      <c r="D25" s="43" t="inlineStr">
+        <is>
+          <t>276-283</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>Rule is disabled, adding clutter and potential confusion.</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr">
+        <is>
+          <t>Remove disabled rules that are no longer needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>Missing Rule Description</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="inlineStr">
+        <is>
+          <t>Temp-AllowAll-Legacy</t>
+        </is>
+      </c>
+      <c r="D26" s="42" t="inlineStr">
+        <is>
+          <t>222-229</t>
+        </is>
+      </c>
+      <c r="E26" s="18" t="inlineStr">
+        <is>
+          <t>No description is set; future reviewers cannot determine the rule's purpose.</t>
+        </is>
+      </c>
+      <c r="F26" s="18" t="inlineStr">
+        <is>
+          <t>Add a description stating the business owner and intent of the rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>Missing Rule Description</t>
+        </is>
+      </c>
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>Internal-DMZ-Access</t>
+        </is>
+      </c>
+      <c r="D27" s="43" t="inlineStr">
+        <is>
+          <t>263-270</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>No description is set; future reviewers cannot determine the rule's purpose.</t>
+        </is>
+      </c>
+      <c r="F27" s="21" t="inlineStr">
+        <is>
+          <t>Add a description stating the business owner and intent of the rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>Missing Rule Description</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="inlineStr">
+        <is>
+          <t>Old-FTP-Rule</t>
+        </is>
+      </c>
+      <c r="D28" s="42" t="inlineStr">
+        <is>
+          <t>276-283</t>
+        </is>
+      </c>
+      <c r="E28" s="18" t="inlineStr">
+        <is>
+          <t>No description is set; future reviewers cannot determine the rule's purpose.</t>
+        </is>
+      </c>
+      <c r="F28" s="18" t="inlineStr">
+        <is>
+          <t>Add a description stating the business owner and intent of the rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="B29" s="21" t="inlineStr">
+        <is>
+          <t>Missing Rule Description</t>
+        </is>
+      </c>
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>Block-Except-Partners</t>
+        </is>
+      </c>
+      <c r="D29" s="43" t="inlineStr">
+        <is>
+          <t>305-313</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>No description is set; future reviewers cannot determine the rule's purpose.</t>
+        </is>
+      </c>
+      <c r="F29" s="21" t="inlineStr">
+        <is>
+          <t>Add a description stating the business owner and intent of the rule.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>No Login Banner</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="D30" s="42" t="inlineStr"/>
+      <c r="E30" s="18" t="inlineStr">
+        <is>
+          <t>No login banner is configured on the management interface.</t>
+        </is>
+      </c>
+      <c r="F30" s="18" t="inlineStr">
+        <is>
+          <t>Add a legal warning banner (login-banner) to satisfy compliance requirements and establish notice of unauthorized access.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="40" t="inlineStr">
+        <is>
+          <t>CIS 4.7 — Manage Default Accounts on Enterprise Assets and Software</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="41" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="B33" s="41" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C33" s="41" t="inlineStr">
+        <is>
+          <t>Rule / Object</t>
+        </is>
+      </c>
+      <c r="D33" s="41" t="inlineStr">
+        <is>
+          <t>Config Line(s)</t>
+        </is>
+      </c>
+      <c r="E33" s="41" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F33" s="41" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>Default/Weak SNMP Community String</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>SNMP</t>
+        </is>
+      </c>
+      <c r="D34" s="42" t="inlineStr"/>
+      <c r="E34" s="18" t="inlineStr">
+        <is>
+          <t>SNMP community string is set to the well-known default value 'public'.</t>
+        </is>
+      </c>
+      <c r="F34" s="18" t="inlineStr">
+        <is>
+          <t>Change the community string to a long random value and restrict allowed SNMP hosts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="40" t="inlineStr">
+        <is>
+          <t>CIS 4.8 — Disable Unnecessary Services on Enterprise Assets and Software</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="44" t="inlineStr">
+        <is>
+          <t>No findings for this control</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="40" t="inlineStr">
+        <is>
+          <t>CIS 4.9 — Configure Trusted DNS Servers on Enterprise Assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="44" t="inlineStr">
+        <is>
+          <t>No findings for this control</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="22" customHeight="1">
+      <c r="A42" s="40" t="inlineStr">
+        <is>
+          <t>CIS 5.2 — Use Unique Passwords</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="41" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="B43" s="41" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C43" s="41" t="inlineStr">
+        <is>
+          <t>Rule / Object</t>
+        </is>
+      </c>
+      <c r="D43" s="41" t="inlineStr">
+        <is>
+          <t>Config Line(s)</t>
+        </is>
+      </c>
+      <c r="E43" s="41" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F43" s="41" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="36" customHeight="1">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>Admin Account Has No Password</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>Admin: operator</t>
+        </is>
+      </c>
+      <c r="D44" s="42" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="E44" s="18" t="inlineStr">
+        <is>
+          <t>Administrator 'operator' has no password hash or SSH key set.</t>
+        </is>
+      </c>
+      <c r="F44" s="18" t="inlineStr">
+        <is>
+          <t>Set a strong password or SSH key for this account immediately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="22" customHeight="1">
+      <c r="A46" s="40" t="inlineStr">
+        <is>
+          <t>CIS 5.4 — Restrict Administrator Privileges to Dedicated Accounts</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="44" t="inlineStr">
+        <is>
+          <t>No findings for this control</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="40" t="inlineStr">
+        <is>
+          <t>CIS 6.5 — Require MFA for Administrative Access</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="41" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="B50" s="41" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C50" s="41" t="inlineStr">
+        <is>
+          <t>Rule / Object</t>
+        </is>
+      </c>
+      <c r="D50" s="41" t="inlineStr">
+        <is>
+          <t>Config Line(s)</t>
+        </is>
+      </c>
+      <c r="E50" s="41" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F50" s="41" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1">
+      <c r="A51" s="9" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="B51" s="21" t="inlineStr">
+        <is>
+          <t>Admin Account Has No Password</t>
+        </is>
+      </c>
+      <c r="C51" s="21" t="inlineStr">
+        <is>
+          <t>Admin: operator</t>
+        </is>
+      </c>
+      <c r="D51" s="43" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="E51" s="21" t="inlineStr">
+        <is>
+          <t>Administrator 'operator' has no password hash or SSH key set.</t>
+        </is>
+      </c>
+      <c r="F51" s="21" t="inlineStr">
+        <is>
+          <t>Set a strong password or SSH key for this account immediately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="36" customHeight="1">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>Admin Without Authentication Profile</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="inlineStr">
+        <is>
+          <t>Admin: admin</t>
+        </is>
+      </c>
+      <c r="D52" s="42" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E52" s="18" t="inlineStr">
+        <is>
+          <t>Administrator 'admin' has no authentication profile — local password only, no MFA.</t>
+        </is>
+      </c>
+      <c r="F52" s="18" t="inlineStr">
+        <is>
+          <t>Assign an authentication profile with MFA to all admin accounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="36" customHeight="1">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B53" s="21" t="inlineStr">
+        <is>
+          <t>Admin Without Authentication Profile</t>
+        </is>
+      </c>
+      <c r="C53" s="21" t="inlineStr">
+        <is>
+          <t>Admin: admin2</t>
+        </is>
+      </c>
+      <c r="D53" s="43" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="E53" s="21" t="inlineStr">
+        <is>
+          <t>Administrator 'admin2' has no authentication profile — local password only, no MFA.</t>
+        </is>
+      </c>
+      <c r="F53" s="21" t="inlineStr">
+        <is>
+          <t>Assign an authentication profile with MFA to all admin accounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="36" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>Admin Without Authentication Profile</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="inlineStr">
+        <is>
+          <t>Admin: operator</t>
+        </is>
+      </c>
+      <c r="D54" s="42" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="E54" s="18" t="inlineStr">
+        <is>
+          <t>Administrator 'operator' has no authentication profile — local password only, no MFA.</t>
+        </is>
+      </c>
+      <c r="F54" s="18" t="inlineStr">
+        <is>
+          <t>Assign an authentication profile with MFA to all admin accounts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="40" t="inlineStr">
+        <is>
+          <t>CIS 6.7 — Centralize Access Control</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="41" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="B57" s="41" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C57" s="41" t="inlineStr">
+        <is>
+          <t>Rule / Object</t>
+        </is>
+      </c>
+      <c r="D57" s="41" t="inlineStr">
+        <is>
+          <t>Config Line(s)</t>
+        </is>
+      </c>
+      <c r="E57" s="41" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F57" s="41" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="36" customHeight="1">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B58" s="18" t="inlineStr">
+        <is>
+          <t>SNMP Enabled Without Source Restrictions</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="inlineStr">
+        <is>
+          <t>SNMP</t>
+        </is>
+      </c>
+      <c r="D58" s="42" t="inlineStr"/>
+      <c r="E58" s="18" t="inlineStr">
+        <is>
+          <t>SNMP is enabled and no management permitted-ip list is configured.</t>
+        </is>
+      </c>
+      <c r="F58" s="18" t="inlineStr">
+        <is>
+          <t>Restrict SNMP access to specific NMS hosts via permitted-ip or ACL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="36" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B59" s="21" t="inlineStr">
+        <is>
+          <t>No Management IP Restrictions</t>
+        </is>
+      </c>
+      <c r="C59" s="21" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="D59" s="43" t="inlineStr"/>
+      <c r="E59" s="21" t="inlineStr">
+        <is>
+          <t>No permitted-ip entries restrict which hosts can reach the management interface.</t>
+        </is>
+      </c>
+      <c r="F59" s="21" t="inlineStr">
+        <is>
+          <t>Add permitted-ip entries to restrict management access to known admin hosts/subnets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="40" t="inlineStr">
+        <is>
+          <t>CIS 6.8 — Define and Maintain Role-Based Access Control</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="44" t="inlineStr">
+        <is>
+          <t>No findings for this control</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="A64" s="40" t="inlineStr">
+        <is>
+          <t>CIS 8.2 — Collect Audit Logs</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="41" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="B65" s="41" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C65" s="41" t="inlineStr">
+        <is>
+          <t>Rule / Object</t>
+        </is>
+      </c>
+      <c r="D65" s="41" t="inlineStr">
+        <is>
+          <t>Config Line(s)</t>
+        </is>
+      </c>
+      <c r="E65" s="41" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F65" s="41" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="36" customHeight="1">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B66" s="18" t="inlineStr">
+        <is>
+          <t>No Logging Configured</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="inlineStr">
+        <is>
+          <t>Temp-AllowAll-Legacy</t>
+        </is>
+      </c>
+      <c r="D66" s="42" t="inlineStr">
+        <is>
+          <t>222-229</t>
+        </is>
+      </c>
+      <c r="E66" s="18" t="inlineStr">
+        <is>
+          <t>Both log-at-session-start and log-at-session-end are disabled.</t>
+        </is>
+      </c>
+      <c r="F66" s="18" t="inlineStr">
+        <is>
+          <t>Enable at minimum log-at-session-end on all rules for audit visibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="36" customHeight="1">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B67" s="21" t="inlineStr">
+        <is>
+          <t>No Logging Configured</t>
+        </is>
+      </c>
+      <c r="C67" s="21" t="inlineStr">
+        <is>
+          <t>Internal-DMZ-Access</t>
+        </is>
+      </c>
+      <c r="D67" s="43" t="inlineStr">
+        <is>
+          <t>263-270</t>
+        </is>
+      </c>
+      <c r="E67" s="21" t="inlineStr">
+        <is>
+          <t>Both log-at-session-start and log-at-session-end are disabled.</t>
+        </is>
+      </c>
+      <c r="F67" s="21" t="inlineStr">
+        <is>
+          <t>Enable at minimum log-at-session-end on all rules for audit visibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="36" customHeight="1">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B68" s="18" t="inlineStr">
+        <is>
+          <t>No Syslog Servers Configured</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="D68" s="42" t="inlineStr"/>
+      <c r="E68" s="18" t="inlineStr">
+        <is>
+          <t>No syslog servers are defined; firewall logs may only reside on the local device.</t>
+        </is>
+      </c>
+      <c r="F68" s="18" t="inlineStr">
+        <is>
+          <t>Configure at least one remote syslog server (preferably two) for log retention, correlation, and incident response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="40" t="inlineStr">
+        <is>
+          <t>CIS 8.4 — Standardize Time Synchronization</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="41" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="B71" s="41" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C71" s="41" t="inlineStr">
+        <is>
+          <t>Rule / Object</t>
+        </is>
+      </c>
+      <c r="D71" s="41" t="inlineStr">
+        <is>
+          <t>Config Line(s)</t>
+        </is>
+      </c>
+      <c r="E71" s="41" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F71" s="41" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="36" customHeight="1">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B72" s="18" t="inlineStr">
+        <is>
+          <t>NTP Not Configured</t>
+        </is>
+      </c>
+      <c r="C72" s="18" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="D72" s="42" t="inlineStr"/>
+      <c r="E72" s="18" t="inlineStr">
+        <is>
+          <t>No primary NTP server is configured.</t>
+        </is>
+      </c>
+      <c r="F72" s="18" t="inlineStr">
+        <is>
+          <t>Configure at least two NTP servers for accurate timestamps in logs and certificates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="22" customHeight="1">
+      <c r="A74" s="40" t="inlineStr">
+        <is>
+          <t>CIS 8.5 — Collect Detailed Audit Logs</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="41" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="B75" s="41" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C75" s="41" t="inlineStr">
+        <is>
+          <t>Rule / Object</t>
+        </is>
+      </c>
+      <c r="D75" s="41" t="inlineStr">
+        <is>
+          <t>Config Line(s)</t>
+        </is>
+      </c>
+      <c r="E75" s="41" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F75" s="41" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="36" customHeight="1">
+      <c r="A76" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B76" s="18" t="inlineStr">
+        <is>
+          <t>No Logging Configured</t>
+        </is>
+      </c>
+      <c r="C76" s="18" t="inlineStr">
+        <is>
+          <t>Temp-AllowAll-Legacy</t>
+        </is>
+      </c>
+      <c r="D76" s="42" t="inlineStr">
+        <is>
+          <t>222-229</t>
+        </is>
+      </c>
+      <c r="E76" s="18" t="inlineStr">
+        <is>
+          <t>Both log-at-session-start and log-at-session-end are disabled.</t>
+        </is>
+      </c>
+      <c r="F76" s="18" t="inlineStr">
+        <is>
+          <t>Enable at minimum log-at-session-end on all rules for audit visibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="36" customHeight="1">
+      <c r="A77" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B77" s="21" t="inlineStr">
+        <is>
+          <t>No Logging Configured</t>
+        </is>
+      </c>
+      <c r="C77" s="21" t="inlineStr">
+        <is>
+          <t>Internal-DMZ-Access</t>
+        </is>
+      </c>
+      <c r="D77" s="43" t="inlineStr">
+        <is>
+          <t>263-270</t>
+        </is>
+      </c>
+      <c r="E77" s="21" t="inlineStr">
+        <is>
+          <t>Both log-at-session-start and log-at-session-end are disabled.</t>
+        </is>
+      </c>
+      <c r="F77" s="21" t="inlineStr">
+        <is>
+          <t>Enable at minimum log-at-session-end on all rules for audit visibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="40" t="inlineStr">
+        <is>
+          <t>CIS 8.9 — Centralize Audit Logs</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="41" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="B80" s="41" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C80" s="41" t="inlineStr">
+        <is>
+          <t>Rule / Object</t>
+        </is>
+      </c>
+      <c r="D80" s="41" t="inlineStr">
+        <is>
+          <t>Config Line(s)</t>
+        </is>
+      </c>
+      <c r="E80" s="41" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F80" s="41" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="36" customHeight="1">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B81" s="21" t="inlineStr">
+        <is>
+          <t>No Syslog Servers Configured</t>
+        </is>
+      </c>
+      <c r="C81" s="21" t="inlineStr">
+        <is>
+          <t>Logging</t>
+        </is>
+      </c>
+      <c r="D81" s="43" t="inlineStr"/>
+      <c r="E81" s="21" t="inlineStr">
+        <is>
+          <t>No syslog servers are defined; firewall logs may only reside on the local device.</t>
+        </is>
+      </c>
+      <c r="F81" s="21" t="inlineStr">
+        <is>
+          <t>Configure at least one remote syslog server (preferably two) for log retention, correlation, and incident response.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="A83" s="40" t="inlineStr">
+        <is>
+          <t>CIS 10.1 — Deploy and Maintain Anti-Malware Software</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="41" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="B84" s="41" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C84" s="41" t="inlineStr">
+        <is>
+          <t>Rule / Object</t>
+        </is>
+      </c>
+      <c r="D84" s="41" t="inlineStr">
+        <is>
+          <t>Config Line(s)</t>
+        </is>
+      </c>
+      <c r="E84" s="41" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F84" s="41" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="36" customHeight="1">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B85" s="21" t="inlineStr">
+        <is>
+          <t>Missing Security Profiles</t>
+        </is>
+      </c>
+      <c r="C85" s="21" t="inlineStr">
+        <is>
+          <t>Temp-AllowAll-Legacy</t>
+        </is>
+      </c>
+      <c r="D85" s="43" t="inlineStr">
+        <is>
+          <t>222-229</t>
+        </is>
+      </c>
+      <c r="E85" s="21" t="inlineStr">
+        <is>
+          <t>Allow rule has no Antivirus / IPS / Anti-Spyware profile.</t>
+        </is>
+      </c>
+      <c r="F85" s="21" t="inlineStr">
+        <is>
+          <t>Attach a security profile group with AV, Vulnerability, and Spyware profiles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="36" customHeight="1">
+      <c r="A86" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B86" s="18" t="inlineStr">
+        <is>
+          <t>Missing Security Profiles</t>
+        </is>
+      </c>
+      <c r="C86" s="18" t="inlineStr">
+        <is>
+          <t>Allow-Partner-Access</t>
+        </is>
+      </c>
+      <c r="D86" s="42" t="inlineStr">
+        <is>
+          <t>235-245</t>
+        </is>
+      </c>
+      <c r="E86" s="18" t="inlineStr">
+        <is>
+          <t>Allow rule has no Antivirus / IPS / Anti-Spyware profile.</t>
+        </is>
+      </c>
+      <c r="F86" s="18" t="inlineStr">
+        <is>
+          <t>Attach a security profile group with AV, Vulnerability, and Spyware profiles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="36" customHeight="1">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B87" s="21" t="inlineStr">
+        <is>
+          <t>Missing Security Profiles</t>
+        </is>
+      </c>
+      <c r="C87" s="21" t="inlineStr">
+        <is>
+          <t>Allow-RDP-Everywhere</t>
+        </is>
+      </c>
+      <c r="D87" s="43" t="inlineStr">
+        <is>
+          <t>249-259</t>
+        </is>
+      </c>
+      <c r="E87" s="21" t="inlineStr">
+        <is>
+          <t>Allow rule has no Antivirus / IPS / Anti-Spyware profile.</t>
+        </is>
+      </c>
+      <c r="F87" s="21" t="inlineStr">
+        <is>
+          <t>Attach a security profile group with AV, Vulnerability, and Spyware profiles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="36" customHeight="1">
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B88" s="18" t="inlineStr">
+        <is>
+          <t>Missing Security Profiles</t>
+        </is>
+      </c>
+      <c r="C88" s="18" t="inlineStr">
+        <is>
+          <t>Internal-DMZ-Access</t>
+        </is>
+      </c>
+      <c r="D88" s="42" t="inlineStr">
+        <is>
+          <t>263-270</t>
+        </is>
+      </c>
+      <c r="E88" s="18" t="inlineStr">
+        <is>
+          <t>Allow rule has no Antivirus / IPS / Anti-Spyware profile.</t>
+        </is>
+      </c>
+      <c r="F88" s="18" t="inlineStr">
+        <is>
+          <t>Attach a security profile group with AV, Vulnerability, and Spyware profiles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="36" customHeight="1">
+      <c r="A89" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B89" s="21" t="inlineStr">
+        <is>
+          <t>Inbound Allow Without Inspection</t>
+        </is>
+      </c>
+      <c r="C89" s="21" t="inlineStr">
+        <is>
+          <t>Allow-Partner-Access</t>
+        </is>
+      </c>
+      <c r="D89" s="43" t="inlineStr">
+        <is>
+          <t>235-245</t>
+        </is>
+      </c>
+      <c r="E89" s="21" t="inlineStr">
+        <is>
+          <t>Inbound rule (external→internal) allows traffic with no AV/IPS/Spyware profiles.</t>
+        </is>
+      </c>
+      <c r="F89" s="21" t="inlineStr">
+        <is>
+          <t>Apply a security profile group with AV, Vulnerability, and Spyware to all inbound rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="36" customHeight="1">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B90" s="18" t="inlineStr">
+        <is>
+          <t>Inbound Allow Without Inspection</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="inlineStr">
+        <is>
+          <t>Allow-RDP-Everywhere</t>
+        </is>
+      </c>
+      <c r="D90" s="42" t="inlineStr">
+        <is>
+          <t>249-259</t>
+        </is>
+      </c>
+      <c r="E90" s="18" t="inlineStr">
+        <is>
+          <t>Inbound rule (external→internal) allows traffic with no AV/IPS/Spyware profiles.</t>
+        </is>
+      </c>
+      <c r="F90" s="18" t="inlineStr">
+        <is>
+          <t>Apply a security profile group with AV, Vulnerability, and Spyware to all inbound rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="22" customHeight="1">
+      <c r="A92" s="40" t="inlineStr">
+        <is>
+          <t>CIS 10.7 — Use Behavior-Based Anti-Malware Software</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="44" t="inlineStr">
+        <is>
+          <t>No findings for this control</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="22" customHeight="1">
+      <c r="A95" s="40" t="inlineStr">
+        <is>
+          <t>CIS 12.2 — Establish and Maintain a Secure Network Architecture</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96" s="41" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="B96" s="41" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C96" s="41" t="inlineStr">
+        <is>
+          <t>Rule / Object</t>
+        </is>
+      </c>
+      <c r="D96" s="41" t="inlineStr">
+        <is>
+          <t>Config Line(s)</t>
+        </is>
+      </c>
+      <c r="E96" s="41" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F96" s="41" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="36" customHeight="1">
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="B97" s="21" t="inlineStr">
+        <is>
+          <t>Any/Any/Any Allow Rule</t>
+        </is>
+      </c>
+      <c r="C97" s="21" t="inlineStr">
+        <is>
+          <t>Temp-AllowAll-Legacy</t>
+        </is>
+      </c>
+      <c r="D97" s="43" t="inlineStr">
+        <is>
+          <t>222-229</t>
+        </is>
+      </c>
+      <c r="E97" s="21" t="inlineStr">
+        <is>
+          <t>Rule allows ALL applications from ANY source to ANY destination.</t>
+        </is>
+      </c>
+      <c r="F97" s="21" t="inlineStr">
+        <is>
+          <t>Apply least-privilege: restrict source, destination, and application.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="36" customHeight="1">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B98" s="18" t="inlineStr">
+        <is>
+          <t>Unrestricted Source Address</t>
+        </is>
+      </c>
+      <c r="C98" s="18" t="inlineStr">
+        <is>
+          <t>Allow-Inbound-HTTPS</t>
+        </is>
+      </c>
+      <c r="D98" s="42" t="inlineStr">
+        <is>
+          <t>207-218</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="inlineStr">
+        <is>
+          <t>Allow rule permits traffic from any source IP.</t>
+        </is>
+      </c>
+      <c r="F98" s="18" t="inlineStr">
+        <is>
+          <t>Restrict the source to specific trusted IP ranges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="36" customHeight="1">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B99" s="21" t="inlineStr">
+        <is>
+          <t>Exposed RDP from Any Source</t>
+        </is>
+      </c>
+      <c r="C99" s="21" t="inlineStr">
+        <is>
+          <t>Allow-RDP-Everywhere</t>
+        </is>
+      </c>
+      <c r="D99" s="43" t="inlineStr">
+        <is>
+          <t>249-259</t>
+        </is>
+      </c>
+      <c r="E99" s="21" t="inlineStr">
+        <is>
+          <t>RDP allowed from any source — high brute-force/ransomware risk.</t>
+        </is>
+      </c>
+      <c r="F99" s="21" t="inlineStr">
+        <is>
+          <t>Restrict to management hosts or require VPN before RDP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="36" customHeight="1">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B100" s="18" t="inlineStr">
+        <is>
+          <t>Negated Source Address</t>
+        </is>
+      </c>
+      <c r="C100" s="18" t="inlineStr">
+        <is>
+          <t>Block-Except-Partners</t>
+        </is>
+      </c>
+      <c r="D100" s="42" t="inlineStr">
+        <is>
+          <t>305-313</t>
+        </is>
+      </c>
+      <c r="E100" s="18" t="inlineStr">
+        <is>
+          <t>Rule uses a negated source — all IPs *except* the listed ones match.</t>
+        </is>
+      </c>
+      <c r="F100" s="18" t="inlineStr">
+        <is>
+          <t>Confirm this is intentional; consider rewriting as explicit allow/deny pairs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="36" customHeight="1">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B101" s="21" t="inlineStr">
+        <is>
+          <t>Potential Shadow Rule</t>
+        </is>
+      </c>
+      <c r="C101" s="21" t="inlineStr">
+        <is>
+          <t>Allow-Partner-Access</t>
+        </is>
+      </c>
+      <c r="D101" s="43" t="inlineStr">
+        <is>
+          <t>235-245</t>
+        </is>
+      </c>
+      <c r="E101" s="21" t="inlineStr">
+        <is>
+          <t>Rule may never be matched because rule 'Temp-AllowAll-Legacy' (#2) already covers its traffic.</t>
+        </is>
+      </c>
+      <c r="F101" s="21" t="inlineStr">
+        <is>
+          <t>Review rule order and remove or reorder as appropriate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="36" customHeight="1">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B102" s="18" t="inlineStr">
+        <is>
+          <t>Potential Shadow Rule</t>
+        </is>
+      </c>
+      <c r="C102" s="18" t="inlineStr">
+        <is>
+          <t>Allow-RDP-Everywhere</t>
+        </is>
+      </c>
+      <c r="D102" s="42" t="inlineStr">
+        <is>
+          <t>249-259</t>
+        </is>
+      </c>
+      <c r="E102" s="18" t="inlineStr">
+        <is>
+          <t>Rule may never be matched because rule 'Temp-AllowAll-Legacy' (#2) already covers its traffic.</t>
+        </is>
+      </c>
+      <c r="F102" s="18" t="inlineStr">
+        <is>
+          <t>Review rule order and remove or reorder as appropriate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="36" customHeight="1">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B103" s="21" t="inlineStr">
+        <is>
+          <t>Potential Shadow Rule</t>
+        </is>
+      </c>
+      <c r="C103" s="21" t="inlineStr">
+        <is>
+          <t>Internal-DMZ-Access</t>
+        </is>
+      </c>
+      <c r="D103" s="43" t="inlineStr">
+        <is>
+          <t>263-270</t>
+        </is>
+      </c>
+      <c r="E103" s="21" t="inlineStr">
+        <is>
+          <t>Rule may never be matched because rule 'Temp-AllowAll-Legacy' (#2) already covers its traffic.</t>
+        </is>
+      </c>
+      <c r="F103" s="21" t="inlineStr">
+        <is>
+          <t>Review rule order and remove or reorder as appropriate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="36" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B104" s="18" t="inlineStr">
+        <is>
+          <t>Potential Shadow Rule</t>
+        </is>
+      </c>
+      <c r="C104" s="18" t="inlineStr">
+        <is>
+          <t>Allow-Outbound-Internet</t>
+        </is>
+      </c>
+      <c r="D104" s="42" t="inlineStr">
+        <is>
+          <t>290-301</t>
+        </is>
+      </c>
+      <c r="E104" s="18" t="inlineStr">
+        <is>
+          <t>Rule may never be matched because rule 'Temp-AllowAll-Legacy' (#2) already covers its traffic.</t>
+        </is>
+      </c>
+      <c r="F104" s="18" t="inlineStr">
+        <is>
+          <t>Review rule order and remove or reorder as appropriate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="22" customHeight="1">
+      <c r="A106" s="40" t="inlineStr">
+        <is>
+          <t>CIS 12.3 — Securely Manage Network Infrastructure</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="41" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="B107" s="41" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C107" s="41" t="inlineStr">
+        <is>
+          <t>Rule / Object</t>
+        </is>
+      </c>
+      <c r="D107" s="41" t="inlineStr">
+        <is>
+          <t>Config Line(s)</t>
+        </is>
+      </c>
+      <c r="E107" s="41" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F107" s="41" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="36" customHeight="1">
+      <c r="A108" s="9" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="B108" s="18" t="inlineStr">
+        <is>
+          <t>Default/Weak SNMP Community String</t>
+        </is>
+      </c>
+      <c r="C108" s="18" t="inlineStr">
+        <is>
+          <t>SNMP</t>
+        </is>
+      </c>
+      <c r="D108" s="42" t="inlineStr"/>
+      <c r="E108" s="18" t="inlineStr">
+        <is>
+          <t>SNMP community string is set to the well-known default value 'public'.</t>
+        </is>
+      </c>
+      <c r="F108" s="18" t="inlineStr">
+        <is>
+          <t>Change the community string to a long random value and restrict allowed SNMP hosts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="36" customHeight="1">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B109" s="21" t="inlineStr">
+        <is>
+          <t>HTTP Management Enabled</t>
+        </is>
+      </c>
+      <c r="C109" s="21" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="D109" s="43" t="inlineStr"/>
+      <c r="E109" s="21" t="inlineStr">
+        <is>
+          <t>HTTP access to the management interface is enabled (cleartext).</t>
+        </is>
+      </c>
+      <c r="F109" s="21" t="inlineStr">
+        <is>
+          <t>Disable HTTP management: set service/disable-http to yes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="36" customHeight="1">
+      <c r="A110" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B110" s="18" t="inlineStr">
+        <is>
+          <t>Telnet Management Enabled</t>
+        </is>
+      </c>
+      <c r="C110" s="18" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="D110" s="42" t="inlineStr"/>
+      <c r="E110" s="18" t="inlineStr">
+        <is>
+          <t>Telnet access to the management interface is enabled (cleartext).</t>
+        </is>
+      </c>
+      <c r="F110" s="18" t="inlineStr">
+        <is>
+          <t>Disable Telnet management: set service/disable-telnet to yes. Use SSH instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="36" customHeight="1">
+      <c r="A111" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B111" s="21" t="inlineStr">
+        <is>
+          <t>SNMP Enabled Without Source Restrictions</t>
+        </is>
+      </c>
+      <c r="C111" s="21" t="inlineStr">
+        <is>
+          <t>SNMP</t>
+        </is>
+      </c>
+      <c r="D111" s="43" t="inlineStr"/>
+      <c r="E111" s="21" t="inlineStr">
+        <is>
+          <t>SNMP is enabled and no management permitted-ip list is configured.</t>
+        </is>
+      </c>
+      <c r="F111" s="21" t="inlineStr">
+        <is>
+          <t>Restrict SNMP access to specific NMS hosts via permitted-ip or ACL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="36" customHeight="1">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B112" s="18" t="inlineStr">
+        <is>
+          <t>No Management IP Restrictions</t>
+        </is>
+      </c>
+      <c r="C112" s="18" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="D112" s="42" t="inlineStr"/>
+      <c r="E112" s="18" t="inlineStr">
+        <is>
+          <t>No permitted-ip entries restrict which hosts can reach the management interface.</t>
+        </is>
+      </c>
+      <c r="F112" s="18" t="inlineStr">
+        <is>
+          <t>Add permitted-ip entries to restrict management access to known admin hosts/subnets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="36" customHeight="1">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B113" s="21" t="inlineStr">
+        <is>
+          <t>SNMPv2c Enabled</t>
+        </is>
+      </c>
+      <c r="C113" s="21" t="inlineStr">
+        <is>
+          <t>SNMP</t>
+        </is>
+      </c>
+      <c r="D113" s="43" t="inlineStr"/>
+      <c r="E113" s="21" t="inlineStr">
+        <is>
+          <t>SNMPv2c is enabled; community strings are transmitted in cleartext.</t>
+        </is>
+      </c>
+      <c r="F113" s="21" t="inlineStr">
+        <is>
+          <t>Migrate to SNMPv3 with authPriv. If SNMPv2c is required, restrict source IPs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="22" customHeight="1">
+      <c r="A115" s="40" t="inlineStr">
+        <is>
+          <t>CIS 12.6 — Use Secure Network Management and Communication Protocols</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="20" customHeight="1">
+      <c r="A116" s="41" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="B116" s="41" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C116" s="41" t="inlineStr">
+        <is>
+          <t>Rule / Object</t>
+        </is>
+      </c>
+      <c r="D116" s="41" t="inlineStr">
+        <is>
+          <t>Config Line(s)</t>
+        </is>
+      </c>
+      <c r="E116" s="41" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F116" s="41" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="36" customHeight="1">
+      <c r="A117" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B117" s="21" t="inlineStr">
+        <is>
+          <t>Exposed RDP from Any Source</t>
+        </is>
+      </c>
+      <c r="C117" s="21" t="inlineStr">
+        <is>
+          <t>Allow-RDP-Everywhere</t>
+        </is>
+      </c>
+      <c r="D117" s="43" t="inlineStr">
+        <is>
+          <t>249-259</t>
+        </is>
+      </c>
+      <c r="E117" s="21" t="inlineStr">
+        <is>
+          <t>RDP allowed from any source — high brute-force/ransomware risk.</t>
+        </is>
+      </c>
+      <c r="F117" s="21" t="inlineStr">
+        <is>
+          <t>Restrict to management hosts or require VPN before RDP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="36" customHeight="1">
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B118" s="18" t="inlineStr">
+        <is>
+          <t>Weak IKE Encryption</t>
+        </is>
+      </c>
+      <c r="C118" s="18" t="inlineStr">
+        <is>
+          <t>IKE Profile: weak-ike-profile</t>
+        </is>
+      </c>
+      <c r="D118" s="42" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E118" s="18" t="inlineStr">
+        <is>
+          <t>IKE crypto profile 'weak-ike-profile' uses 3DES encryption.</t>
+        </is>
+      </c>
+      <c r="F118" s="18" t="inlineStr">
+        <is>
+          <t>Replace 3DES with AES-256-GCM or AES-256-CBC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="36" customHeight="1">
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B119" s="21" t="inlineStr">
+        <is>
+          <t>Weak IKE Hash/PRF</t>
+        </is>
+      </c>
+      <c r="C119" s="21" t="inlineStr">
+        <is>
+          <t>IKE Profile: weak-ike-profile</t>
+        </is>
+      </c>
+      <c r="D119" s="43" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E119" s="21" t="inlineStr">
+        <is>
+          <t>IKE crypto profile 'weak-ike-profile' uses MD5 for integrity/PRF.</t>
+        </is>
+      </c>
+      <c r="F119" s="21" t="inlineStr">
+        <is>
+          <t>Replace MD5 with SHA-256, SHA-384, or SHA-512.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="36" customHeight="1">
+      <c r="A120" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B120" s="18" t="inlineStr">
+        <is>
+          <t>Weak IKE DH Group</t>
+        </is>
+      </c>
+      <c r="C120" s="18" t="inlineStr">
+        <is>
+          <t>IKE Profile: weak-ike-profile</t>
+        </is>
+      </c>
+      <c r="D120" s="42" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E120" s="18" t="inlineStr">
+        <is>
+          <t>IKE crypto profile 'weak-ike-profile' includes group2 (insufficient key size).</t>
+        </is>
+      </c>
+      <c r="F120" s="18" t="inlineStr">
+        <is>
+          <t>Use DH Group 14 (2048-bit) minimum; prefer Group 19/20 (ECDH-256/384).</t>
+        </is>
+      </c>
+    </row>
+    <row r="121" ht="36" customHeight="1">
+      <c r="A121" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B121" s="21" t="inlineStr">
+        <is>
+          <t>Weak IPSec Encryption</t>
+        </is>
+      </c>
+      <c r="C121" s="21" t="inlineStr">
+        <is>
+          <t>IPSec Profile: weak-ipsec-profile</t>
+        </is>
+      </c>
+      <c r="D121" s="43" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E121" s="21" t="inlineStr">
+        <is>
+          <t>IPSec crypto profile 'weak-ipsec-profile' uses 3DES for ESP encryption.</t>
+        </is>
+      </c>
+      <c r="F121" s="21" t="inlineStr">
+        <is>
+          <t>Replace 3DES with AES-256-GCM (preferred) or AES-256-CBC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="36" customHeight="1">
+      <c r="A122" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B122" s="18" t="inlineStr">
+        <is>
+          <t>Weak IPSec Authentication</t>
+        </is>
+      </c>
+      <c r="C122" s="18" t="inlineStr">
+        <is>
+          <t>IPSec Profile: weak-ipsec-profile</t>
+        </is>
+      </c>
+      <c r="D122" s="42" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E122" s="18" t="inlineStr">
+        <is>
+          <t>IPSec crypto profile 'weak-ipsec-profile' uses MD5 for ESP authentication.</t>
+        </is>
+      </c>
+      <c r="F122" s="18" t="inlineStr">
+        <is>
+          <t>Replace MD5 with SHA-256 or higher.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="36" customHeight="1">
+      <c r="A123" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B123" s="21" t="inlineStr">
+        <is>
+          <t>Weak IPSec DH Group (PFS)</t>
+        </is>
+      </c>
+      <c r="C123" s="21" t="inlineStr">
+        <is>
+          <t>IPSec Profile: weak-ipsec-profile</t>
+        </is>
+      </c>
+      <c r="D123" s="43" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E123" s="21" t="inlineStr">
+        <is>
+          <t>IPSec profile 'weak-ipsec-profile' uses group2 for Perfect Forward Secrecy.</t>
+        </is>
+      </c>
+      <c r="F123" s="21" t="inlineStr">
+        <is>
+          <t>Use DH Group 14 minimum for PFS; prefer Group 19/20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="36" customHeight="1">
+      <c r="A124" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B124" s="18" t="inlineStr">
+        <is>
+          <t>Weak Minimum TLS Version</t>
+        </is>
+      </c>
+      <c r="C124" s="18" t="inlineStr">
+        <is>
+          <t>SSL/TLS Profile: old-tls-profile</t>
+        </is>
+      </c>
+      <c r="D124" s="42" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E124" s="18" t="inlineStr">
+        <is>
+          <t>SSL/TLS profile 'old-tls-profile' allows TLS1.0 connections.</t>
+        </is>
+      </c>
+      <c r="F124" s="18" t="inlineStr">
+        <is>
+          <t>Set minimum version to TLS 1.2; prefer TLS 1.3 where supported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="36" customHeight="1">
+      <c r="A125" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B125" s="21" t="inlineStr">
+        <is>
+          <t>HTTP Management Enabled</t>
+        </is>
+      </c>
+      <c r="C125" s="21" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="D125" s="43" t="inlineStr"/>
+      <c r="E125" s="21" t="inlineStr">
+        <is>
+          <t>HTTP access to the management interface is enabled (cleartext).</t>
+        </is>
+      </c>
+      <c r="F125" s="21" t="inlineStr">
+        <is>
+          <t>Disable HTTP management: set service/disable-http to yes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="36" customHeight="1">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B126" s="18" t="inlineStr">
+        <is>
+          <t>Telnet Management Enabled</t>
+        </is>
+      </c>
+      <c r="C126" s="18" t="inlineStr">
+        <is>
+          <t>Management</t>
+        </is>
+      </c>
+      <c r="D126" s="42" t="inlineStr"/>
+      <c r="E126" s="18" t="inlineStr">
+        <is>
+          <t>Telnet access to the management interface is enabled (cleartext).</t>
+        </is>
+      </c>
+      <c r="F126" s="18" t="inlineStr">
+        <is>
+          <t>Disable Telnet management: set service/disable-telnet to yes. Use SSH instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="36" customHeight="1">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B127" s="21" t="inlineStr">
+        <is>
+          <t>Weak IKE Hash/PRF</t>
+        </is>
+      </c>
+      <c r="C127" s="21" t="inlineStr">
+        <is>
+          <t>IKE Profile: weak-ike-profile</t>
+        </is>
+      </c>
+      <c r="D127" s="43" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E127" s="21" t="inlineStr">
+        <is>
+          <t>IKE crypto profile 'weak-ike-profile' uses SHA1 for integrity/PRF.</t>
+        </is>
+      </c>
+      <c r="F127" s="21" t="inlineStr">
+        <is>
+          <t>Replace SHA1 with SHA-256, SHA-384, or SHA-512.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="22" customHeight="1">
+      <c r="A129" s="40" t="inlineStr">
+        <is>
+          <t>CIS 13.10 — Perform Application Layer Filtering</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="20" customHeight="1">
+      <c r="A130" s="41" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="B130" s="41" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C130" s="41" t="inlineStr">
+        <is>
+          <t>Rule / Object</t>
+        </is>
+      </c>
+      <c r="D130" s="41" t="inlineStr">
+        <is>
+          <t>Config Line(s)</t>
+        </is>
+      </c>
+      <c r="E130" s="41" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F130" s="41" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="36" customHeight="1">
+      <c r="A131" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B131" s="21" t="inlineStr">
+        <is>
+          <t>Missing Security Profiles</t>
+        </is>
+      </c>
+      <c r="C131" s="21" t="inlineStr">
+        <is>
+          <t>Temp-AllowAll-Legacy</t>
+        </is>
+      </c>
+      <c r="D131" s="43" t="inlineStr">
+        <is>
+          <t>222-229</t>
+        </is>
+      </c>
+      <c r="E131" s="21" t="inlineStr">
+        <is>
+          <t>Allow rule has no Antivirus / IPS / Anti-Spyware profile.</t>
+        </is>
+      </c>
+      <c r="F131" s="21" t="inlineStr">
+        <is>
+          <t>Attach a security profile group with AV, Vulnerability, and Spyware profiles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="36" customHeight="1">
+      <c r="A132" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B132" s="18" t="inlineStr">
+        <is>
+          <t>Missing Security Profiles</t>
+        </is>
+      </c>
+      <c r="C132" s="18" t="inlineStr">
+        <is>
+          <t>Allow-Partner-Access</t>
+        </is>
+      </c>
+      <c r="D132" s="42" t="inlineStr">
+        <is>
+          <t>235-245</t>
+        </is>
+      </c>
+      <c r="E132" s="18" t="inlineStr">
+        <is>
+          <t>Allow rule has no Antivirus / IPS / Anti-Spyware profile.</t>
+        </is>
+      </c>
+      <c r="F132" s="18" t="inlineStr">
+        <is>
+          <t>Attach a security profile group with AV, Vulnerability, and Spyware profiles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="36" customHeight="1">
+      <c r="A133" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B133" s="21" t="inlineStr">
+        <is>
+          <t>Missing Security Profiles</t>
+        </is>
+      </c>
+      <c r="C133" s="21" t="inlineStr">
+        <is>
+          <t>Allow-RDP-Everywhere</t>
+        </is>
+      </c>
+      <c r="D133" s="43" t="inlineStr">
+        <is>
+          <t>249-259</t>
+        </is>
+      </c>
+      <c r="E133" s="21" t="inlineStr">
+        <is>
+          <t>Allow rule has no Antivirus / IPS / Anti-Spyware profile.</t>
+        </is>
+      </c>
+      <c r="F133" s="21" t="inlineStr">
+        <is>
+          <t>Attach a security profile group with AV, Vulnerability, and Spyware profiles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="36" customHeight="1">
+      <c r="A134" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B134" s="18" t="inlineStr">
+        <is>
+          <t>Missing Security Profiles</t>
+        </is>
+      </c>
+      <c r="C134" s="18" t="inlineStr">
+        <is>
+          <t>Internal-DMZ-Access</t>
+        </is>
+      </c>
+      <c r="D134" s="42" t="inlineStr">
+        <is>
+          <t>263-270</t>
+        </is>
+      </c>
+      <c r="E134" s="18" t="inlineStr">
+        <is>
+          <t>Allow rule has no Antivirus / IPS / Anti-Spyware profile.</t>
+        </is>
+      </c>
+      <c r="F134" s="18" t="inlineStr">
+        <is>
+          <t>Attach a security profile group with AV, Vulnerability, and Spyware profiles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="22" customHeight="1">
+      <c r="A136" s="40" t="inlineStr">
+        <is>
+          <t>CIS 13.3 — Deploy a Network Intrusion Detection Solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="20" customHeight="1">
+      <c r="A137" s="41" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="B137" s="41" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C137" s="41" t="inlineStr">
+        <is>
+          <t>Rule / Object</t>
+        </is>
+      </c>
+      <c r="D137" s="41" t="inlineStr">
+        <is>
+          <t>Config Line(s)</t>
+        </is>
+      </c>
+      <c r="E137" s="41" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F137" s="41" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="36" customHeight="1">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B138" s="18" t="inlineStr">
+        <is>
+          <t>Zone Missing Protection Profile</t>
+        </is>
+      </c>
+      <c r="C138" s="18" t="inlineStr">
+        <is>
+          <t>Zone: untrust</t>
+        </is>
+      </c>
+      <c r="D138" s="42" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="E138" s="18" t="inlineStr">
+        <is>
+          <t>Zone 'untrust' has no Zone Protection Profile (DoS, flood, recon protection).</t>
+        </is>
+      </c>
+      <c r="F138" s="18" t="inlineStr">
+        <is>
+          <t>Assign a Zone Protection Profile — especially critical for external/untrust zones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="22" customHeight="1">
+      <c r="A140" s="40" t="inlineStr">
+        <is>
+          <t>CIS 13.4 — Perform Traffic Filtering Between Network Segments</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="20" customHeight="1">
+      <c r="A141" s="41" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="B141" s="41" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C141" s="41" t="inlineStr">
+        <is>
+          <t>Rule / Object</t>
+        </is>
+      </c>
+      <c r="D141" s="41" t="inlineStr">
+        <is>
+          <t>Config Line(s)</t>
+        </is>
+      </c>
+      <c r="E141" s="41" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F141" s="41" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="36" customHeight="1">
+      <c r="A142" s="9" t="inlineStr">
+        <is>
+          <t>CRITICAL</t>
+        </is>
+      </c>
+      <c r="B142" s="18" t="inlineStr">
+        <is>
+          <t>Any/Any/Any Allow Rule</t>
+        </is>
+      </c>
+      <c r="C142" s="18" t="inlineStr">
+        <is>
+          <t>Temp-AllowAll-Legacy</t>
+        </is>
+      </c>
+      <c r="D142" s="42" t="inlineStr">
+        <is>
+          <t>222-229</t>
+        </is>
+      </c>
+      <c r="E142" s="18" t="inlineStr">
+        <is>
+          <t>Rule allows ALL applications from ANY source to ANY destination.</t>
+        </is>
+      </c>
+      <c r="F142" s="18" t="inlineStr">
+        <is>
+          <t>Apply least-privilege: restrict source, destination, and application.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="36" customHeight="1">
+      <c r="A143" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B143" s="21" t="inlineStr">
+        <is>
+          <t>Unrestricted Source Address</t>
+        </is>
+      </c>
+      <c r="C143" s="21" t="inlineStr">
+        <is>
+          <t>Allow-Inbound-HTTPS</t>
+        </is>
+      </c>
+      <c r="D143" s="43" t="inlineStr">
+        <is>
+          <t>207-218</t>
+        </is>
+      </c>
+      <c r="E143" s="21" t="inlineStr">
+        <is>
+          <t>Allow rule permits traffic from any source IP.</t>
+        </is>
+      </c>
+      <c r="F143" s="21" t="inlineStr">
+        <is>
+          <t>Restrict the source to specific trusted IP ranges.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="36" customHeight="1">
+      <c r="A144" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B144" s="18" t="inlineStr">
+        <is>
+          <t>Inbound Allow Without Inspection</t>
+        </is>
+      </c>
+      <c r="C144" s="18" t="inlineStr">
+        <is>
+          <t>Allow-Partner-Access</t>
+        </is>
+      </c>
+      <c r="D144" s="42" t="inlineStr">
+        <is>
+          <t>235-245</t>
+        </is>
+      </c>
+      <c r="E144" s="18" t="inlineStr">
+        <is>
+          <t>Inbound rule (external→internal) allows traffic with no AV/IPS/Spyware profiles.</t>
+        </is>
+      </c>
+      <c r="F144" s="18" t="inlineStr">
+        <is>
+          <t>Apply a security profile group with AV, Vulnerability, and Spyware to all inbound rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="36" customHeight="1">
+      <c r="A145" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B145" s="21" t="inlineStr">
+        <is>
+          <t>Inbound Allow Without Inspection</t>
+        </is>
+      </c>
+      <c r="C145" s="21" t="inlineStr">
+        <is>
+          <t>Allow-RDP-Everywhere</t>
+        </is>
+      </c>
+      <c r="D145" s="43" t="inlineStr">
+        <is>
+          <t>249-259</t>
+        </is>
+      </c>
+      <c r="E145" s="21" t="inlineStr">
+        <is>
+          <t>Inbound rule (external→internal) allows traffic with no AV/IPS/Spyware profiles.</t>
+        </is>
+      </c>
+      <c r="F145" s="21" t="inlineStr">
+        <is>
+          <t>Apply a security profile group with AV, Vulnerability, and Spyware to all inbound rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="36" customHeight="1">
+      <c r="A146" s="11" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B146" s="18" t="inlineStr">
+        <is>
+          <t>Zone Missing Protection Profile</t>
+        </is>
+      </c>
+      <c r="C146" s="18" t="inlineStr">
+        <is>
+          <t>Zone: untrust</t>
+        </is>
+      </c>
+      <c r="D146" s="42" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="E146" s="18" t="inlineStr">
+        <is>
+          <t>Zone 'untrust' has no Zone Protection Profile (DoS, flood, recon protection).</t>
+        </is>
+      </c>
+      <c r="F146" s="18" t="inlineStr">
+        <is>
+          <t>Assign a Zone Protection Profile — especially critical for external/untrust zones.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="22" customHeight="1">
+      <c r="A148" s="40" t="inlineStr">
+        <is>
+          <t>CIS 13.8 — Deploy a Network Intrusion Prevention Solution</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="20" customHeight="1">
+      <c r="A149" s="41" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="B149" s="41" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C149" s="41" t="inlineStr">
+        <is>
+          <t>Rule / Object</t>
+        </is>
+      </c>
+      <c r="D149" s="41" t="inlineStr">
+        <is>
+          <t>Config Line(s)</t>
+        </is>
+      </c>
+      <c r="E149" s="41" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F149" s="41" t="inlineStr">
+        <is>
+          <t>Recommendation</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="36" customHeight="1">
+      <c r="A150" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B150" s="18" t="inlineStr">
+        <is>
+          <t>Missing Security Profiles</t>
+        </is>
+      </c>
+      <c r="C150" s="18" t="inlineStr">
+        <is>
+          <t>Temp-AllowAll-Legacy</t>
+        </is>
+      </c>
+      <c r="D150" s="42" t="inlineStr">
+        <is>
+          <t>222-229</t>
+        </is>
+      </c>
+      <c r="E150" s="18" t="inlineStr">
+        <is>
+          <t>Allow rule has no Antivirus / IPS / Anti-Spyware profile.</t>
+        </is>
+      </c>
+      <c r="F150" s="18" t="inlineStr">
+        <is>
+          <t>Attach a security profile group with AV, Vulnerability, and Spyware profiles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="36" customHeight="1">
+      <c r="A151" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B151" s="21" t="inlineStr">
+        <is>
+          <t>Missing Security Profiles</t>
+        </is>
+      </c>
+      <c r="C151" s="21" t="inlineStr">
+        <is>
+          <t>Allow-Partner-Access</t>
+        </is>
+      </c>
+      <c r="D151" s="43" t="inlineStr">
+        <is>
+          <t>235-245</t>
+        </is>
+      </c>
+      <c r="E151" s="21" t="inlineStr">
+        <is>
+          <t>Allow rule has no Antivirus / IPS / Anti-Spyware profile.</t>
+        </is>
+      </c>
+      <c r="F151" s="21" t="inlineStr">
+        <is>
+          <t>Attach a security profile group with AV, Vulnerability, and Spyware profiles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="36" customHeight="1">
+      <c r="A152" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B152" s="18" t="inlineStr">
+        <is>
+          <t>Missing Security Profiles</t>
+        </is>
+      </c>
+      <c r="C152" s="18" t="inlineStr">
+        <is>
+          <t>Allow-RDP-Everywhere</t>
+        </is>
+      </c>
+      <c r="D152" s="42" t="inlineStr">
+        <is>
+          <t>249-259</t>
+        </is>
+      </c>
+      <c r="E152" s="18" t="inlineStr">
+        <is>
+          <t>Allow rule has no Antivirus / IPS / Anti-Spyware profile.</t>
+        </is>
+      </c>
+      <c r="F152" s="18" t="inlineStr">
+        <is>
+          <t>Attach a security profile group with AV, Vulnerability, and Spyware profiles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="36" customHeight="1">
+      <c r="A153" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B153" s="21" t="inlineStr">
+        <is>
+          <t>Missing Security Profiles</t>
+        </is>
+      </c>
+      <c r="C153" s="21" t="inlineStr">
+        <is>
+          <t>Internal-DMZ-Access</t>
+        </is>
+      </c>
+      <c r="D153" s="43" t="inlineStr">
+        <is>
+          <t>263-270</t>
+        </is>
+      </c>
+      <c r="E153" s="21" t="inlineStr">
+        <is>
+          <t>Allow rule has no Antivirus / IPS / Anti-Spyware profile.</t>
+        </is>
+      </c>
+      <c r="F153" s="21" t="inlineStr">
+        <is>
+          <t>Attach a security profile group with AV, Vulnerability, and Spyware profiles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="36" customHeight="1">
+      <c r="A154" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B154" s="18" t="inlineStr">
+        <is>
+          <t>Inbound Allow Without Inspection</t>
+        </is>
+      </c>
+      <c r="C154" s="18" t="inlineStr">
+        <is>
+          <t>Allow-Partner-Access</t>
+        </is>
+      </c>
+      <c r="D154" s="42" t="inlineStr">
+        <is>
+          <t>235-245</t>
+        </is>
+      </c>
+      <c r="E154" s="18" t="inlineStr">
+        <is>
+          <t>Inbound rule (external→internal) allows traffic with no AV/IPS/Spyware profiles.</t>
+        </is>
+      </c>
+      <c r="F154" s="18" t="inlineStr">
+        <is>
+          <t>Apply a security profile group with AV, Vulnerability, and Spyware to all inbound rules.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="36" customHeight="1">
+      <c r="A155" s="10" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="B155" s="21" t="inlineStr">
+        <is>
+          <t>Inbound Allow Without Inspection</t>
+        </is>
+      </c>
+      <c r="C155" s="21" t="inlineStr">
+        <is>
+          <t>Allow-RDP-Everywhere</t>
+        </is>
+      </c>
+      <c r="D155" s="43" t="inlineStr">
+        <is>
+          <t>249-259</t>
+        </is>
+      </c>
+      <c r="E155" s="21" t="inlineStr">
+        <is>
+          <t>Inbound rule (external→internal) allows traffic with no AV/IPS/Spyware profiles.</t>
+        </is>
+      </c>
+      <c r="F155" s="21" t="inlineStr">
+        <is>
+          <t>Apply a security profile group with AV, Vulnerability, and Spyware to all inbound rules.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="30">
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A136:F136"/>
+    <mergeCell ref="A74:F74"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A95:F95"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A129:F129"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A106:F106"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="A140:F140"/>
+    <mergeCell ref="A115:F115"/>
+    <mergeCell ref="A93:F93"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A148:F148"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="A61:F61"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3891,7 +7410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H44"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3899,9 +7418,10 @@
     <col width="32" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="62" customWidth="1" min="6" max="6"/>
-    <col width="62" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -3932,15 +7452,20 @@
       </c>
       <c r="F1" s="8" t="inlineStr">
         <is>
+          <t>CIS v8 Controls</t>
+        </is>
+      </c>
+      <c r="G1" s="8" t="inlineStr">
+        <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="G1" s="8" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>Recommendation</t>
         </is>
       </c>
-      <c r="H1" s="8" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>Details</t>
         </is>
@@ -3970,17 +7495,22 @@
           <t>222-229</t>
         </is>
       </c>
-      <c r="F2" s="18" t="inlineStr">
+      <c r="F2" s="36" t="inlineStr">
+        <is>
+          <t>CIS 12.2 · CIS 13.4</t>
+        </is>
+      </c>
+      <c r="G2" s="18" t="inlineStr">
         <is>
           <t>Rule allows ALL applications from ANY source to ANY destination.</t>
         </is>
       </c>
-      <c r="G2" s="18" t="inlineStr">
+      <c r="H2" s="18" t="inlineStr">
         <is>
           <t>Apply least-privilege: restrict source, destination, and application.</t>
         </is>
       </c>
-      <c r="H2" s="18" t="inlineStr">
+      <c r="I2" s="18" t="inlineStr">
         <is>
           <t>Zones: any → any</t>
         </is>
@@ -4005,22 +7535,27 @@
           <t>Admin: operator</t>
         </is>
       </c>
-      <c r="E3" s="36" t="inlineStr">
+      <c r="E3" s="37" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F3" s="21" t="inlineStr">
+      <c r="F3" s="38" t="inlineStr">
+        <is>
+          <t>CIS 5.2 · CIS 6.5</t>
+        </is>
+      </c>
+      <c r="G3" s="21" t="inlineStr">
         <is>
           <t>Administrator 'operator' has no password hash or SSH key set.</t>
         </is>
       </c>
-      <c r="G3" s="21" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t>Set a strong password or SSH key for this account immediately.</t>
         </is>
       </c>
-      <c r="H3" s="21" t="inlineStr">
+      <c r="I3" s="21" t="inlineStr">
         <is>
           <t>Role: custom</t>
         </is>
@@ -4046,17 +7581,22 @@
         </is>
       </c>
       <c r="E4" s="35" t="inlineStr"/>
-      <c r="F4" s="18" t="inlineStr">
+      <c r="F4" s="36" t="inlineStr">
+        <is>
+          <t>CIS 4.7 · CIS 12.3</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
         <is>
           <t>SNMP community string is set to the well-known default value 'public'.</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr">
+      <c r="H4" s="18" t="inlineStr">
         <is>
           <t>Change the community string to a long random value and restrict allowed SNMP hosts.</t>
         </is>
       </c>
-      <c r="H4" s="18" t="inlineStr"/>
+      <c r="I4" s="18" t="inlineStr"/>
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" s="15" t="n">
@@ -4077,22 +7617,27 @@
           <t>Temp-AllowAll-Legacy</t>
         </is>
       </c>
-      <c r="E5" s="36" t="inlineStr">
+      <c r="E5" s="37" t="inlineStr">
         <is>
           <t>222-229</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="F5" s="38" t="inlineStr">
+        <is>
+          <t>CIS 10.1 · CIS 13.8 · CIS 13.10</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>Allow rule has no Antivirus / IPS / Anti-Spyware profile.</t>
         </is>
       </c>
-      <c r="G5" s="21" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>Attach a security profile group with AV, Vulnerability, and Spyware profiles.</t>
         </is>
       </c>
-      <c r="H5" s="21" t="inlineStr">
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>App: any  Svc: any</t>
         </is>
@@ -4122,17 +7667,22 @@
           <t>235-245</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="36" t="inlineStr">
+        <is>
+          <t>CIS 10.1 · CIS 13.8 · CIS 13.10</t>
+        </is>
+      </c>
+      <c r="G6" s="18" t="inlineStr">
         <is>
           <t>Allow rule has no Antivirus / IPS / Anti-Spyware profile.</t>
         </is>
       </c>
-      <c r="G6" s="18" t="inlineStr">
+      <c r="H6" s="18" t="inlineStr">
         <is>
           <t>Attach a security profile group with AV, Vulnerability, and Spyware profiles.</t>
         </is>
       </c>
-      <c r="H6" s="18" t="inlineStr">
+      <c r="I6" s="18" t="inlineStr">
         <is>
           <t>App: any  Svc: svc-https</t>
         </is>
@@ -4157,22 +7707,27 @@
           <t>Allow-RDP-Everywhere</t>
         </is>
       </c>
-      <c r="E7" s="36" t="inlineStr">
+      <c r="E7" s="37" t="inlineStr">
         <is>
           <t>249-259</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F7" s="38" t="inlineStr">
+        <is>
+          <t>CIS 10.1 · CIS 13.8 · CIS 13.10</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr">
         <is>
           <t>Allow rule has no Antivirus / IPS / Anti-Spyware profile.</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>Attach a security profile group with AV, Vulnerability, and Spyware profiles.</t>
         </is>
       </c>
-      <c r="H7" s="21" t="inlineStr">
+      <c r="I7" s="21" t="inlineStr">
         <is>
           <t>App: rdp  Svc: application-default</t>
         </is>
@@ -4202,17 +7757,22 @@
           <t>263-270</t>
         </is>
       </c>
-      <c r="F8" s="18" t="inlineStr">
+      <c r="F8" s="36" t="inlineStr">
+        <is>
+          <t>CIS 10.1 · CIS 13.8 · CIS 13.10</t>
+        </is>
+      </c>
+      <c r="G8" s="18" t="inlineStr">
         <is>
           <t>Allow rule has no Antivirus / IPS / Anti-Spyware profile.</t>
         </is>
       </c>
-      <c r="G8" s="18" t="inlineStr">
+      <c r="H8" s="18" t="inlineStr">
         <is>
           <t>Attach a security profile group with AV, Vulnerability, and Spyware profiles.</t>
         </is>
       </c>
-      <c r="H8" s="18" t="inlineStr">
+      <c r="I8" s="18" t="inlineStr">
         <is>
           <t>App: ssh  Svc: application-default</t>
         </is>
@@ -4237,22 +7797,27 @@
           <t>Temp-AllowAll-Legacy</t>
         </is>
       </c>
-      <c r="E9" s="36" t="inlineStr">
+      <c r="E9" s="37" t="inlineStr">
         <is>
           <t>222-229</t>
         </is>
       </c>
-      <c r="F9" s="21" t="inlineStr">
+      <c r="F9" s="38" t="inlineStr">
+        <is>
+          <t>CIS 8.2 · CIS 8.5</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>Both log-at-session-start and log-at-session-end are disabled.</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t>Enable at minimum log-at-session-end on all rules for audit visibility.</t>
         </is>
       </c>
-      <c r="H9" s="21" t="inlineStr">
+      <c r="I9" s="21" t="inlineStr">
         <is>
           <t>Action: allow</t>
         </is>
@@ -4282,17 +7847,22 @@
           <t>263-270</t>
         </is>
       </c>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="F10" s="36" t="inlineStr">
+        <is>
+          <t>CIS 8.2 · CIS 8.5</t>
+        </is>
+      </c>
+      <c r="G10" s="18" t="inlineStr">
         <is>
           <t>Both log-at-session-start and log-at-session-end are disabled.</t>
         </is>
       </c>
-      <c r="G10" s="18" t="inlineStr">
+      <c r="H10" s="18" t="inlineStr">
         <is>
           <t>Enable at minimum log-at-session-end on all rules for audit visibility.</t>
         </is>
       </c>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="I10" s="18" t="inlineStr">
         <is>
           <t>Action: allow</t>
         </is>
@@ -4317,22 +7887,27 @@
           <t>Allow-Inbound-HTTPS</t>
         </is>
       </c>
-      <c r="E11" s="36" t="inlineStr">
+      <c r="E11" s="37" t="inlineStr">
         <is>
           <t>207-218</t>
         </is>
       </c>
-      <c r="F11" s="21" t="inlineStr">
+      <c r="F11" s="38" t="inlineStr">
+        <is>
+          <t>CIS 12.2 · CIS 13.4</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr">
         <is>
           <t>Allow rule permits traffic from any source IP.</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t>Restrict the source to specific trusted IP ranges.</t>
         </is>
       </c>
-      <c r="H11" s="21" t="inlineStr">
+      <c r="I11" s="21" t="inlineStr">
         <is>
           <t>Dest: web-server-1  App: ssl, web-browsing</t>
         </is>
@@ -4362,17 +7937,22 @@
           <t>249-259</t>
         </is>
       </c>
-      <c r="F12" s="18" t="inlineStr">
+      <c r="F12" s="36" t="inlineStr">
+        <is>
+          <t>CIS 12.2 · CIS 12.6</t>
+        </is>
+      </c>
+      <c r="G12" s="18" t="inlineStr">
         <is>
           <t>RDP allowed from any source — high brute-force/ransomware risk.</t>
         </is>
       </c>
-      <c r="G12" s="18" t="inlineStr">
+      <c r="H12" s="18" t="inlineStr">
         <is>
           <t>Restrict to management hosts or require VPN before RDP.</t>
         </is>
       </c>
-      <c r="H12" s="18" t="inlineStr">
+      <c r="I12" s="18" t="inlineStr">
         <is>
           <t>Src zones: untrust</t>
         </is>
@@ -4397,22 +7977,27 @@
           <t>Allow-Partner-Access</t>
         </is>
       </c>
-      <c r="E13" s="36" t="inlineStr">
+      <c r="E13" s="37" t="inlineStr">
         <is>
           <t>235-245</t>
         </is>
       </c>
-      <c r="F13" s="21" t="inlineStr">
+      <c r="F13" s="38" t="inlineStr">
+        <is>
+          <t>CIS 10.1 · CIS 13.4 · CIS 13.8</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr">
         <is>
           <t>Inbound rule (external→internal) allows traffic with no AV/IPS/Spyware profiles.</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t>Apply a security profile group with AV, Vulnerability, and Spyware to all inbound rules.</t>
         </is>
       </c>
-      <c r="H13" s="21" t="inlineStr">
+      <c r="I13" s="21" t="inlineStr">
         <is>
           <t>Zones: untrust → trust</t>
         </is>
@@ -4442,17 +8027,22 @@
           <t>249-259</t>
         </is>
       </c>
-      <c r="F14" s="18" t="inlineStr">
+      <c r="F14" s="36" t="inlineStr">
+        <is>
+          <t>CIS 10.1 · CIS 13.4 · CIS 13.8</t>
+        </is>
+      </c>
+      <c r="G14" s="18" t="inlineStr">
         <is>
           <t>Inbound rule (external→internal) allows traffic with no AV/IPS/Spyware profiles.</t>
         </is>
       </c>
-      <c r="G14" s="18" t="inlineStr">
+      <c r="H14" s="18" t="inlineStr">
         <is>
           <t>Apply a security profile group with AV, Vulnerability, and Spyware to all inbound rules.</t>
         </is>
       </c>
-      <c r="H14" s="18" t="inlineStr">
+      <c r="I14" s="18" t="inlineStr">
         <is>
           <t>Zones: untrust → trust</t>
         </is>
@@ -4477,22 +8067,27 @@
           <t>IKE Profile: weak-ike-profile</t>
         </is>
       </c>
-      <c r="E15" s="36" t="inlineStr">
+      <c r="E15" s="37" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="F15" s="21" t="inlineStr">
+      <c r="F15" s="38" t="inlineStr">
+        <is>
+          <t>CIS 3.10 · CIS 12.6</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr">
         <is>
           <t>IKE crypto profile 'weak-ike-profile' uses 3DES encryption.</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t>Replace 3DES with AES-256-GCM or AES-256-CBC.</t>
         </is>
       </c>
-      <c r="H15" s="21" t="inlineStr">
+      <c r="I15" s="21" t="inlineStr">
         <is>
           <t>Encryption list: 3des, aes-128-cbc</t>
         </is>
@@ -4522,17 +8117,22 @@
           <t>38</t>
         </is>
       </c>
-      <c r="F16" s="18" t="inlineStr">
+      <c r="F16" s="36" t="inlineStr">
+        <is>
+          <t>CIS 3.10 · CIS 12.6</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="inlineStr">
         <is>
           <t>IKE crypto profile 'weak-ike-profile' uses MD5 for integrity/PRF.</t>
         </is>
       </c>
-      <c r="G16" s="18" t="inlineStr">
+      <c r="H16" s="18" t="inlineStr">
         <is>
           <t>Replace MD5 with SHA-256, SHA-384, or SHA-512.</t>
         </is>
       </c>
-      <c r="H16" s="18" t="inlineStr">
+      <c r="I16" s="18" t="inlineStr">
         <is>
           <t>Hash list: md5, sha1</t>
         </is>
@@ -4557,22 +8157,27 @@
           <t>IKE Profile: weak-ike-profile</t>
         </is>
       </c>
-      <c r="E17" s="36" t="inlineStr">
+      <c r="E17" s="37" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="F17" s="21" t="inlineStr">
+      <c r="F17" s="38" t="inlineStr">
+        <is>
+          <t>CIS 3.10 · CIS 12.6</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="inlineStr">
         <is>
           <t>IKE crypto profile 'weak-ike-profile' includes group2 (insufficient key size).</t>
         </is>
       </c>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t>Use DH Group 14 (2048-bit) minimum; prefer Group 19/20 (ECDH-256/384).</t>
         </is>
       </c>
-      <c r="H17" s="21" t="inlineStr">
+      <c r="I17" s="21" t="inlineStr">
         <is>
           <t>DH groups: group2, group14</t>
         </is>
@@ -4602,17 +8207,22 @@
           <t>52</t>
         </is>
       </c>
-      <c r="F18" s="18" t="inlineStr">
+      <c r="F18" s="36" t="inlineStr">
+        <is>
+          <t>CIS 3.10 · CIS 12.6</t>
+        </is>
+      </c>
+      <c r="G18" s="18" t="inlineStr">
         <is>
           <t>IPSec crypto profile 'weak-ipsec-profile' uses 3DES for ESP encryption.</t>
         </is>
       </c>
-      <c r="G18" s="18" t="inlineStr">
+      <c r="H18" s="18" t="inlineStr">
         <is>
           <t>Replace 3DES with AES-256-GCM (preferred) or AES-256-CBC.</t>
         </is>
       </c>
-      <c r="H18" s="18" t="inlineStr">
+      <c r="I18" s="18" t="inlineStr">
         <is>
           <t>Encryption list: 3des</t>
         </is>
@@ -4637,22 +8247,27 @@
           <t>IPSec Profile: weak-ipsec-profile</t>
         </is>
       </c>
-      <c r="E19" s="36" t="inlineStr">
+      <c r="E19" s="37" t="inlineStr">
         <is>
           <t>52</t>
         </is>
       </c>
-      <c r="F19" s="21" t="inlineStr">
+      <c r="F19" s="38" t="inlineStr">
+        <is>
+          <t>CIS 3.10 · CIS 12.6</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="inlineStr">
         <is>
           <t>IPSec crypto profile 'weak-ipsec-profile' uses MD5 for ESP authentication.</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="H19" s="21" t="inlineStr">
         <is>
           <t>Replace MD5 with SHA-256 or higher.</t>
         </is>
       </c>
-      <c r="H19" s="21" t="inlineStr">
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>Auth list: md5</t>
         </is>
@@ -4682,17 +8297,22 @@
           <t>52</t>
         </is>
       </c>
-      <c r="F20" s="18" t="inlineStr">
+      <c r="F20" s="36" t="inlineStr">
+        <is>
+          <t>CIS 3.10 · CIS 12.6</t>
+        </is>
+      </c>
+      <c r="G20" s="18" t="inlineStr">
         <is>
           <t>IPSec profile 'weak-ipsec-profile' uses group2 for Perfect Forward Secrecy.</t>
         </is>
       </c>
-      <c r="G20" s="18" t="inlineStr">
+      <c r="H20" s="18" t="inlineStr">
         <is>
           <t>Use DH Group 14 minimum for PFS; prefer Group 19/20.</t>
         </is>
       </c>
-      <c r="H20" s="18" t="inlineStr">
+      <c r="I20" s="18" t="inlineStr">
         <is>
           <t>DH group: group2</t>
         </is>
@@ -4717,22 +8337,27 @@
           <t>SSL/TLS Profile: old-tls-profile</t>
         </is>
       </c>
-      <c r="E21" s="36" t="inlineStr">
+      <c r="E21" s="37" t="inlineStr">
         <is>
           <t>89</t>
         </is>
       </c>
-      <c r="F21" s="21" t="inlineStr">
+      <c r="F21" s="38" t="inlineStr">
+        <is>
+          <t>CIS 3.10 · CIS 12.6</t>
+        </is>
+      </c>
+      <c r="G21" s="21" t="inlineStr">
         <is>
           <t>SSL/TLS profile 'old-tls-profile' allows TLS1.0 connections.</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="H21" s="21" t="inlineStr">
         <is>
           <t>Set minimum version to TLS 1.2; prefer TLS 1.3 where supported.</t>
         </is>
       </c>
-      <c r="H21" s="21" t="inlineStr">
+      <c r="I21" s="21" t="inlineStr">
         <is>
           <t>min-version: tls1-0  max-version: max</t>
         </is>
@@ -4758,17 +8383,22 @@
         </is>
       </c>
       <c r="E22" s="35" t="inlineStr"/>
-      <c r="F22" s="18" t="inlineStr">
+      <c r="F22" s="36" t="inlineStr">
+        <is>
+          <t>CIS 4.2 · CIS 12.3 · CIS 12.6</t>
+        </is>
+      </c>
+      <c r="G22" s="18" t="inlineStr">
         <is>
           <t>HTTP access to the management interface is enabled (cleartext).</t>
         </is>
       </c>
-      <c r="G22" s="18" t="inlineStr">
+      <c r="H22" s="18" t="inlineStr">
         <is>
           <t>Disable HTTP management: set service/disable-http to yes.</t>
         </is>
       </c>
-      <c r="H22" s="18" t="inlineStr">
+      <c r="I22" s="18" t="inlineStr">
         <is>
           <t>Management traffic including credentials sent in plaintext over HTTP.</t>
         </is>
@@ -4793,18 +8423,23 @@
           <t>Management</t>
         </is>
       </c>
-      <c r="E23" s="36" t="inlineStr"/>
-      <c r="F23" s="21" t="inlineStr">
+      <c r="E23" s="37" t="inlineStr"/>
+      <c r="F23" s="38" t="inlineStr">
+        <is>
+          <t>CIS 4.2 · CIS 12.3 · CIS 12.6</t>
+        </is>
+      </c>
+      <c r="G23" s="21" t="inlineStr">
         <is>
           <t>Telnet access to the management interface is enabled (cleartext).</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr">
+      <c r="H23" s="21" t="inlineStr">
         <is>
           <t>Disable Telnet management: set service/disable-telnet to yes. Use SSH instead.</t>
         </is>
       </c>
-      <c r="H23" s="21" t="inlineStr"/>
+      <c r="I23" s="21" t="inlineStr"/>
     </row>
     <row r="24" ht="40" customHeight="1">
       <c r="A24" s="34" t="n">
@@ -4830,17 +8465,22 @@
           <t>99</t>
         </is>
       </c>
-      <c r="F24" s="18" t="inlineStr">
+      <c r="F24" s="36" t="inlineStr">
+        <is>
+          <t>CIS 6.5</t>
+        </is>
+      </c>
+      <c r="G24" s="18" t="inlineStr">
         <is>
           <t>Administrator 'admin' has no authentication profile — local password only, no MFA.</t>
         </is>
       </c>
-      <c r="G24" s="18" t="inlineStr">
+      <c r="H24" s="18" t="inlineStr">
         <is>
           <t>Assign an authentication profile with MFA to all admin accounts.</t>
         </is>
       </c>
-      <c r="H24" s="18" t="inlineStr">
+      <c r="I24" s="18" t="inlineStr">
         <is>
           <t>Role: superuser</t>
         </is>
@@ -4865,22 +8505,27 @@
           <t>Admin: admin2</t>
         </is>
       </c>
-      <c r="E25" s="36" t="inlineStr">
+      <c r="E25" s="37" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="F25" s="21" t="inlineStr">
+      <c r="F25" s="38" t="inlineStr">
+        <is>
+          <t>CIS 6.5</t>
+        </is>
+      </c>
+      <c r="G25" s="21" t="inlineStr">
         <is>
           <t>Administrator 'admin2' has no authentication profile — local password only, no MFA.</t>
         </is>
       </c>
-      <c r="G25" s="21" t="inlineStr">
+      <c r="H25" s="21" t="inlineStr">
         <is>
           <t>Assign an authentication profile with MFA to all admin accounts.</t>
         </is>
       </c>
-      <c r="H25" s="21" t="inlineStr">
+      <c r="I25" s="21" t="inlineStr">
         <is>
           <t>Role: superuser</t>
         </is>
@@ -4910,17 +8555,22 @@
           <t>116</t>
         </is>
       </c>
-      <c r="F26" s="18" t="inlineStr">
+      <c r="F26" s="36" t="inlineStr">
+        <is>
+          <t>CIS 6.5</t>
+        </is>
+      </c>
+      <c r="G26" s="18" t="inlineStr">
         <is>
           <t>Administrator 'operator' has no authentication profile — local password only, no MFA.</t>
         </is>
       </c>
-      <c r="G26" s="18" t="inlineStr">
+      <c r="H26" s="18" t="inlineStr">
         <is>
           <t>Assign an authentication profile with MFA to all admin accounts.</t>
         </is>
       </c>
-      <c r="H26" s="18" t="inlineStr">
+      <c r="I26" s="18" t="inlineStr">
         <is>
           <t>Role: custom</t>
         </is>
@@ -4945,18 +8595,23 @@
           <t>SNMP</t>
         </is>
       </c>
-      <c r="E27" s="36" t="inlineStr"/>
-      <c r="F27" s="21" t="inlineStr">
+      <c r="E27" s="37" t="inlineStr"/>
+      <c r="F27" s="38" t="inlineStr">
+        <is>
+          <t>CIS 12.3 · CIS 6.7</t>
+        </is>
+      </c>
+      <c r="G27" s="21" t="inlineStr">
         <is>
           <t>SNMP is enabled and no management permitted-ip list is configured.</t>
         </is>
       </c>
-      <c r="G27" s="21" t="inlineStr">
+      <c r="H27" s="21" t="inlineStr">
         <is>
           <t>Restrict SNMP access to specific NMS hosts via permitted-ip or ACL.</t>
         </is>
       </c>
-      <c r="H27" s="21" t="inlineStr"/>
+      <c r="I27" s="21" t="inlineStr"/>
     </row>
     <row r="28" ht="40" customHeight="1">
       <c r="A28" s="34" t="n">
@@ -4982,17 +8637,22 @@
           <t>305-313</t>
         </is>
       </c>
-      <c r="F28" s="18" t="inlineStr">
+      <c r="F28" s="36" t="inlineStr">
+        <is>
+          <t>CIS 4.2 · CIS 12.2</t>
+        </is>
+      </c>
+      <c r="G28" s="18" t="inlineStr">
         <is>
           <t>Rule uses a negated source — all IPs *except* the listed ones match.</t>
         </is>
       </c>
-      <c r="G28" s="18" t="inlineStr">
+      <c r="H28" s="18" t="inlineStr">
         <is>
           <t>Confirm this is intentional; consider rewriting as explicit allow/deny pairs.</t>
         </is>
       </c>
-      <c r="H28" s="18" t="inlineStr">
+      <c r="I28" s="18" t="inlineStr">
         <is>
           <t>NOT (partner-net)</t>
         </is>
@@ -5017,22 +8677,27 @@
           <t>Zone: untrust</t>
         </is>
       </c>
-      <c r="E29" s="36" t="inlineStr">
+      <c r="E29" s="37" t="inlineStr">
         <is>
           <t>184</t>
         </is>
       </c>
-      <c r="F29" s="21" t="inlineStr">
+      <c r="F29" s="38" t="inlineStr">
+        <is>
+          <t>CIS 13.3 · CIS 13.4</t>
+        </is>
+      </c>
+      <c r="G29" s="21" t="inlineStr">
         <is>
           <t>Zone 'untrust' has no Zone Protection Profile (DoS, flood, recon protection).</t>
         </is>
       </c>
-      <c r="G29" s="21" t="inlineStr">
+      <c r="H29" s="21" t="inlineStr">
         <is>
           <t>Assign a Zone Protection Profile — especially critical for external/untrust zones.</t>
         </is>
       </c>
-      <c r="H29" s="21" t="inlineStr">
+      <c r="I29" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">Zone type:   Interfaces: </t>
         </is>
@@ -5062,17 +8727,22 @@
           <t>235-245</t>
         </is>
       </c>
-      <c r="F30" s="18" t="inlineStr">
+      <c r="F30" s="36" t="inlineStr">
+        <is>
+          <t>CIS 4.2 · CIS 12.2</t>
+        </is>
+      </c>
+      <c r="G30" s="18" t="inlineStr">
         <is>
           <t>Rule may never be matched because rule 'Temp-AllowAll-Legacy' (#2) already covers its traffic.</t>
         </is>
       </c>
-      <c r="G30" s="18" t="inlineStr">
+      <c r="H30" s="18" t="inlineStr">
         <is>
           <t>Review rule order and remove or reorder as appropriate.</t>
         </is>
       </c>
-      <c r="H30" s="18" t="inlineStr">
+      <c r="I30" s="18" t="inlineStr">
         <is>
           <t>Shadowed by: Temp-AllowAll-Legacy (rule #2)</t>
         </is>
@@ -5097,22 +8767,27 @@
           <t>Allow-RDP-Everywhere</t>
         </is>
       </c>
-      <c r="E31" s="36" t="inlineStr">
+      <c r="E31" s="37" t="inlineStr">
         <is>
           <t>249-259</t>
         </is>
       </c>
-      <c r="F31" s="21" t="inlineStr">
+      <c r="F31" s="38" t="inlineStr">
+        <is>
+          <t>CIS 4.2 · CIS 12.2</t>
+        </is>
+      </c>
+      <c r="G31" s="21" t="inlineStr">
         <is>
           <t>Rule may never be matched because rule 'Temp-AllowAll-Legacy' (#2) already covers its traffic.</t>
         </is>
       </c>
-      <c r="G31" s="21" t="inlineStr">
+      <c r="H31" s="21" t="inlineStr">
         <is>
           <t>Review rule order and remove or reorder as appropriate.</t>
         </is>
       </c>
-      <c r="H31" s="21" t="inlineStr">
+      <c r="I31" s="21" t="inlineStr">
         <is>
           <t>Shadowed by: Temp-AllowAll-Legacy (rule #2)</t>
         </is>
@@ -5142,17 +8817,22 @@
           <t>263-270</t>
         </is>
       </c>
-      <c r="F32" s="18" t="inlineStr">
+      <c r="F32" s="36" t="inlineStr">
+        <is>
+          <t>CIS 4.2 · CIS 12.2</t>
+        </is>
+      </c>
+      <c r="G32" s="18" t="inlineStr">
         <is>
           <t>Rule may never be matched because rule 'Temp-AllowAll-Legacy' (#2) already covers its traffic.</t>
         </is>
       </c>
-      <c r="G32" s="18" t="inlineStr">
+      <c r="H32" s="18" t="inlineStr">
         <is>
           <t>Review rule order and remove or reorder as appropriate.</t>
         </is>
       </c>
-      <c r="H32" s="18" t="inlineStr">
+      <c r="I32" s="18" t="inlineStr">
         <is>
           <t>Shadowed by: Temp-AllowAll-Legacy (rule #2)</t>
         </is>
@@ -5177,22 +8857,27 @@
           <t>Allow-Outbound-Internet</t>
         </is>
       </c>
-      <c r="E33" s="36" t="inlineStr">
+      <c r="E33" s="37" t="inlineStr">
         <is>
           <t>290-301</t>
         </is>
       </c>
-      <c r="F33" s="21" t="inlineStr">
+      <c r="F33" s="38" t="inlineStr">
+        <is>
+          <t>CIS 4.2 · CIS 12.2</t>
+        </is>
+      </c>
+      <c r="G33" s="21" t="inlineStr">
         <is>
           <t>Rule may never be matched because rule 'Temp-AllowAll-Legacy' (#2) already covers its traffic.</t>
         </is>
       </c>
-      <c r="G33" s="21" t="inlineStr">
+      <c r="H33" s="21" t="inlineStr">
         <is>
           <t>Review rule order and remove or reorder as appropriate.</t>
         </is>
       </c>
-      <c r="H33" s="21" t="inlineStr">
+      <c r="I33" s="21" t="inlineStr">
         <is>
           <t>Shadowed by: Temp-AllowAll-Legacy (rule #2)</t>
         </is>
@@ -5222,17 +8907,22 @@
           <t>38</t>
         </is>
       </c>
-      <c r="F34" s="18" t="inlineStr">
+      <c r="F34" s="36" t="inlineStr">
+        <is>
+          <t>CIS 3.10 · CIS 12.6</t>
+        </is>
+      </c>
+      <c r="G34" s="18" t="inlineStr">
         <is>
           <t>IKE crypto profile 'weak-ike-profile' uses SHA1 for integrity/PRF.</t>
         </is>
       </c>
-      <c r="G34" s="18" t="inlineStr">
+      <c r="H34" s="18" t="inlineStr">
         <is>
           <t>Replace SHA1 with SHA-256, SHA-384, or SHA-512.</t>
         </is>
       </c>
-      <c r="H34" s="18" t="inlineStr">
+      <c r="I34" s="18" t="inlineStr">
         <is>
           <t>Hash list: md5, sha1</t>
         </is>
@@ -5257,18 +8947,23 @@
           <t>Management</t>
         </is>
       </c>
-      <c r="E35" s="36" t="inlineStr"/>
-      <c r="F35" s="21" t="inlineStr">
+      <c r="E35" s="37" t="inlineStr"/>
+      <c r="F35" s="38" t="inlineStr">
+        <is>
+          <t>CIS 12.3 · CIS 6.7</t>
+        </is>
+      </c>
+      <c r="G35" s="21" t="inlineStr">
         <is>
           <t>No permitted-ip entries restrict which hosts can reach the management interface.</t>
         </is>
       </c>
-      <c r="G35" s="21" t="inlineStr">
+      <c r="H35" s="21" t="inlineStr">
         <is>
           <t>Add permitted-ip entries to restrict management access to known admin hosts/subnets.</t>
         </is>
       </c>
-      <c r="H35" s="21" t="inlineStr">
+      <c r="I35" s="21" t="inlineStr">
         <is>
           <t>Without restrictions, any host that can route to the mgmt interface can attempt login.</t>
         </is>
@@ -5294,17 +8989,22 @@
         </is>
       </c>
       <c r="E36" s="35" t="inlineStr"/>
-      <c r="F36" s="18" t="inlineStr">
+      <c r="F36" s="36" t="inlineStr">
+        <is>
+          <t>CIS 8.4</t>
+        </is>
+      </c>
+      <c r="G36" s="18" t="inlineStr">
         <is>
           <t>No primary NTP server is configured.</t>
         </is>
       </c>
-      <c r="G36" s="18" t="inlineStr">
+      <c r="H36" s="18" t="inlineStr">
         <is>
           <t>Configure at least two NTP servers for accurate timestamps in logs and certificates.</t>
         </is>
       </c>
-      <c r="H36" s="18" t="inlineStr">
+      <c r="I36" s="18" t="inlineStr">
         <is>
           <t>Inaccurate time breaks certificate validation, log correlation, and TOTP/MFA.</t>
         </is>
@@ -5329,18 +9029,23 @@
           <t>SNMP</t>
         </is>
       </c>
-      <c r="E37" s="36" t="inlineStr"/>
-      <c r="F37" s="21" t="inlineStr">
+      <c r="E37" s="37" t="inlineStr"/>
+      <c r="F37" s="38" t="inlineStr">
+        <is>
+          <t>CIS 4.2 · CIS 12.3</t>
+        </is>
+      </c>
+      <c r="G37" s="21" t="inlineStr">
         <is>
           <t>SNMPv2c is enabled; community strings are transmitted in cleartext.</t>
         </is>
       </c>
-      <c r="G37" s="21" t="inlineStr">
+      <c r="H37" s="21" t="inlineStr">
         <is>
           <t>Migrate to SNMPv3 with authPriv. If SNMPv2c is required, restrict source IPs.</t>
         </is>
       </c>
-      <c r="H37" s="21" t="inlineStr"/>
+      <c r="I37" s="21" t="inlineStr"/>
     </row>
     <row r="38" ht="40" customHeight="1">
       <c r="A38" s="34" t="n">
@@ -5362,17 +9067,22 @@
         </is>
       </c>
       <c r="E38" s="35" t="inlineStr"/>
-      <c r="F38" s="18" t="inlineStr">
+      <c r="F38" s="36" t="inlineStr">
+        <is>
+          <t>CIS 8.2 · CIS 8.9</t>
+        </is>
+      </c>
+      <c r="G38" s="18" t="inlineStr">
         <is>
           <t>No syslog servers are defined; firewall logs may only reside on the local device.</t>
         </is>
       </c>
-      <c r="G38" s="18" t="inlineStr">
+      <c r="H38" s="18" t="inlineStr">
         <is>
           <t>Configure at least one remote syslog server (preferably two) for log retention, correlation, and incident response.</t>
         </is>
       </c>
-      <c r="H38" s="18" t="inlineStr"/>
+      <c r="I38" s="18" t="inlineStr"/>
     </row>
     <row r="39" ht="40" customHeight="1">
       <c r="A39" s="15" t="n">
@@ -5393,22 +9103,27 @@
           <t>Old-FTP-Rule</t>
         </is>
       </c>
-      <c r="E39" s="36" t="inlineStr">
+      <c r="E39" s="37" t="inlineStr">
         <is>
           <t>276-283</t>
         </is>
       </c>
-      <c r="F39" s="21" t="inlineStr">
+      <c r="F39" s="38" t="inlineStr">
+        <is>
+          <t>CIS 4.2</t>
+        </is>
+      </c>
+      <c r="G39" s="21" t="inlineStr">
         <is>
           <t>Rule is disabled, adding clutter and potential confusion.</t>
         </is>
       </c>
-      <c r="G39" s="21" t="inlineStr">
+      <c r="H39" s="21" t="inlineStr">
         <is>
           <t>Remove disabled rules that are no longer needed.</t>
         </is>
       </c>
-      <c r="H39" s="21" t="inlineStr"/>
+      <c r="I39" s="21" t="inlineStr"/>
     </row>
     <row r="40" ht="40" customHeight="1">
       <c r="A40" s="34" t="n">
@@ -5434,17 +9149,22 @@
           <t>222-229</t>
         </is>
       </c>
-      <c r="F40" s="18" t="inlineStr">
+      <c r="F40" s="36" t="inlineStr">
+        <is>
+          <t>CIS 4.2</t>
+        </is>
+      </c>
+      <c r="G40" s="18" t="inlineStr">
         <is>
           <t>No description is set; future reviewers cannot determine the rule's purpose.</t>
         </is>
       </c>
-      <c r="G40" s="18" t="inlineStr">
+      <c r="H40" s="18" t="inlineStr">
         <is>
           <t>Add a description stating the business owner and intent of the rule.</t>
         </is>
       </c>
-      <c r="H40" s="18" t="inlineStr"/>
+      <c r="I40" s="18" t="inlineStr"/>
     </row>
     <row r="41" ht="40" customHeight="1">
       <c r="A41" s="15" t="n">
@@ -5465,22 +9185,27 @@
           <t>Internal-DMZ-Access</t>
         </is>
       </c>
-      <c r="E41" s="36" t="inlineStr">
+      <c r="E41" s="37" t="inlineStr">
         <is>
           <t>263-270</t>
         </is>
       </c>
-      <c r="F41" s="21" t="inlineStr">
+      <c r="F41" s="38" t="inlineStr">
+        <is>
+          <t>CIS 4.2</t>
+        </is>
+      </c>
+      <c r="G41" s="21" t="inlineStr">
         <is>
           <t>No description is set; future reviewers cannot determine the rule's purpose.</t>
         </is>
       </c>
-      <c r="G41" s="21" t="inlineStr">
+      <c r="H41" s="21" t="inlineStr">
         <is>
           <t>Add a description stating the business owner and intent of the rule.</t>
         </is>
       </c>
-      <c r="H41" s="21" t="inlineStr"/>
+      <c r="I41" s="21" t="inlineStr"/>
     </row>
     <row r="42" ht="40" customHeight="1">
       <c r="A42" s="34" t="n">
@@ -5506,17 +9231,22 @@
           <t>276-283</t>
         </is>
       </c>
-      <c r="F42" s="18" t="inlineStr">
+      <c r="F42" s="36" t="inlineStr">
+        <is>
+          <t>CIS 4.2</t>
+        </is>
+      </c>
+      <c r="G42" s="18" t="inlineStr">
         <is>
           <t>No description is set; future reviewers cannot determine the rule's purpose.</t>
         </is>
       </c>
-      <c r="G42" s="18" t="inlineStr">
+      <c r="H42" s="18" t="inlineStr">
         <is>
           <t>Add a description stating the business owner and intent of the rule.</t>
         </is>
       </c>
-      <c r="H42" s="18" t="inlineStr"/>
+      <c r="I42" s="18" t="inlineStr"/>
     </row>
     <row r="43" ht="40" customHeight="1">
       <c r="A43" s="15" t="n">
@@ -5537,22 +9267,27 @@
           <t>Block-Except-Partners</t>
         </is>
       </c>
-      <c r="E43" s="36" t="inlineStr">
+      <c r="E43" s="37" t="inlineStr">
         <is>
           <t>305-313</t>
         </is>
       </c>
-      <c r="F43" s="21" t="inlineStr">
+      <c r="F43" s="38" t="inlineStr">
+        <is>
+          <t>CIS 4.2</t>
+        </is>
+      </c>
+      <c r="G43" s="21" t="inlineStr">
         <is>
           <t>No description is set; future reviewers cannot determine the rule's purpose.</t>
         </is>
       </c>
-      <c r="G43" s="21" t="inlineStr">
+      <c r="H43" s="21" t="inlineStr">
         <is>
           <t>Add a description stating the business owner and intent of the rule.</t>
         </is>
       </c>
-      <c r="H43" s="21" t="inlineStr"/>
+      <c r="I43" s="21" t="inlineStr"/>
     </row>
     <row r="44" ht="40" customHeight="1">
       <c r="A44" s="34" t="n">
@@ -5574,20 +9309,25 @@
         </is>
       </c>
       <c r="E44" s="35" t="inlineStr"/>
-      <c r="F44" s="18" t="inlineStr">
+      <c r="F44" s="36" t="inlineStr">
+        <is>
+          <t>CIS 4.2</t>
+        </is>
+      </c>
+      <c r="G44" s="18" t="inlineStr">
         <is>
           <t>No login banner is configured on the management interface.</t>
         </is>
       </c>
-      <c r="G44" s="18" t="inlineStr">
+      <c r="H44" s="18" t="inlineStr">
         <is>
           <t>Add a legal warning banner (login-banner) to satisfy compliance requirements and establish notice of unauthorized access.</t>
         </is>
       </c>
-      <c r="H44" s="18" t="inlineStr"/>
+      <c r="I44" s="18" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>